--- a/pss-2.0-global/.claude/screen-tracker/SCREEN-STATUS-OVERVIEW.xlsx
+++ b/pss-2.0-global/.claude/screen-tracker/SCREEN-STATUS-OVERVIEW.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repos\PWDS\pwds-soruban\pss-2.0-global\.claude\screen-tracker\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repos\PWDS\pwds-soruban - Copy\pss-2.0-global\.claude\screen-tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1318" uniqueCount="246">
   <si>
     <t>Screen #</t>
   </si>
@@ -1073,7 +1073,106 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="28">
+  <dxfs count="37">
+    <dxf>
+      <font>
+        <color rgb="FF3730A3"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE0E7FF"/>
+          <bgColor rgb="FFE0E7FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF3730A3"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE0E7FF"/>
+          <bgColor rgb="FFE0E7FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF3730A3"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE0E7FF"/>
+          <bgColor rgb="FFE0E7FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF3730A3"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE0E7FF"/>
+          <bgColor rgb="FFE0E7FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF4B5563"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF3F4F6"/>
+          <bgColor rgb="FFF3F4F6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF854D0E"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEF9C3"/>
+          <bgColor rgb="FFFEF9C3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1E40AF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDBEAFE"/>
+          <bgColor rgb="FFDBEAFE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF92400E"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEF3C7"/>
+          <bgColor rgb="FFFEF3C7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF166534"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDCFCE7"/>
+          <bgColor rgb="FFDCFCE7"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF3730A3"/>
@@ -4998,8 +5097,8 @@
       <c r="G107" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H107" s="5" t="s">
-        <v>17</v>
+      <c r="H107" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="I107" s="2" t="s">
         <v>16</v>
@@ -5025,8 +5124,11 @@
       <c r="E108" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F108" s="6" t="s">
-        <v>18</v>
+      <c r="F108" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="H108" s="6" t="s">
         <v>18</v>
@@ -5051,8 +5153,11 @@
       <c r="E109" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F109" s="6" t="s">
-        <v>18</v>
+      <c r="F109" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="H109" s="6" t="s">
         <v>18</v>
@@ -5104,7 +5209,10 @@
         <v>32</v>
       </c>
       <c r="F111" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
+      </c>
+      <c r="G111" t="s">
+        <v>16</v>
       </c>
       <c r="H111" s="6" t="s">
         <v>18</v>
@@ -5442,7 +5550,10 @@
         <v>32</v>
       </c>
       <c r="F124" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
+      </c>
+      <c r="G124" t="s">
+        <v>16</v>
       </c>
       <c r="H124" s="6" t="s">
         <v>18</v>
@@ -5468,7 +5579,10 @@
         <v>32</v>
       </c>
       <c r="F125" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
+      </c>
+      <c r="G125" t="s">
+        <v>16</v>
       </c>
       <c r="H125" s="6" t="s">
         <v>18</v>
@@ -5494,7 +5608,10 @@
         <v>32</v>
       </c>
       <c r="F126" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
+      </c>
+      <c r="G126" t="s">
+        <v>16</v>
       </c>
       <c r="H126" s="6" t="s">
         <v>18</v>
@@ -5520,7 +5637,10 @@
         <v>32</v>
       </c>
       <c r="F127" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
+      </c>
+      <c r="G127" t="s">
+        <v>16</v>
       </c>
       <c r="H127" s="6" t="s">
         <v>18</v>
@@ -5546,7 +5666,10 @@
         <v>32</v>
       </c>
       <c r="F128" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
+      </c>
+      <c r="G128" t="s">
+        <v>16</v>
       </c>
       <c r="H128" s="6" t="s">
         <v>18</v>
@@ -5572,7 +5695,10 @@
         <v>32</v>
       </c>
       <c r="F129" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
+      </c>
+      <c r="G129" t="s">
+        <v>16</v>
       </c>
       <c r="H129" s="6" t="s">
         <v>18</v>
@@ -5598,7 +5724,10 @@
         <v>32</v>
       </c>
       <c r="F130" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
+      </c>
+      <c r="G130" t="s">
+        <v>16</v>
       </c>
       <c r="H130" s="6" t="s">
         <v>18</v>
@@ -5624,7 +5753,10 @@
         <v>32</v>
       </c>
       <c r="F131" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
+      </c>
+      <c r="G131" t="s">
+        <v>16</v>
       </c>
       <c r="H131" s="6" t="s">
         <v>18</v>
@@ -5650,7 +5782,10 @@
         <v>32</v>
       </c>
       <c r="F132" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
+      </c>
+      <c r="G132" t="s">
+        <v>16</v>
       </c>
       <c r="H132" s="6" t="s">
         <v>18</v>
@@ -5676,7 +5811,10 @@
         <v>32</v>
       </c>
       <c r="F133" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
+      </c>
+      <c r="G133" t="s">
+        <v>16</v>
       </c>
       <c r="H133" s="6" t="s">
         <v>18</v>
@@ -5702,7 +5840,10 @@
         <v>32</v>
       </c>
       <c r="F134" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
+      </c>
+      <c r="G134" t="s">
+        <v>16</v>
       </c>
       <c r="H134" s="6" t="s">
         <v>18</v>
@@ -5728,7 +5869,10 @@
         <v>32</v>
       </c>
       <c r="F135" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
+      </c>
+      <c r="G135" t="s">
+        <v>16</v>
       </c>
       <c r="H135" s="6" t="s">
         <v>18</v>
@@ -5754,7 +5898,10 @@
         <v>32</v>
       </c>
       <c r="F136" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
+      </c>
+      <c r="G136" t="s">
+        <v>16</v>
       </c>
       <c r="H136" s="6" t="s">
         <v>18</v>
@@ -5780,7 +5927,10 @@
         <v>32</v>
       </c>
       <c r="F137" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
+      </c>
+      <c r="G137" t="s">
+        <v>16</v>
       </c>
       <c r="H137" s="6" t="s">
         <v>18</v>
@@ -5806,7 +5956,10 @@
         <v>32</v>
       </c>
       <c r="F138" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
+      </c>
+      <c r="G138" t="s">
+        <v>16</v>
       </c>
       <c r="H138" s="6" t="s">
         <v>18</v>
@@ -6181,108 +6334,137 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E2:E152">
-    <cfRule type="cellIs" dxfId="27" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="10" operator="equal">
       <formula>"High"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="11" operator="equal">
       <formula>"Medium"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="12" operator="equal">
       <formula>"Low"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F152">
-    <cfRule type="cellIs" dxfId="24" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="13" operator="equal">
       <formula>"Completed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="14" operator="equal">
       <formula>"Completed - Needs Fix"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="15" operator="equal">
       <formula>"Ready to Build"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="16" operator="equal">
       <formula>"In Progress (Partial)"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="17" operator="equal">
       <formula>"Not Started"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="18" operator="equal">
       <formula>"Upcoming (Dashboard)"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="19" operator="equal">
       <formula>"Upcoming (Config)"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="20" operator="equal">
       <formula>"Upcoming (Mobile)"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="21" operator="equal">
       <formula>"Upcoming"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H152">
-    <cfRule type="cellIs" dxfId="15" priority="13" operator="equal">
+  <conditionalFormatting sqref="H2:H106 H108:H152">
+    <cfRule type="cellIs" dxfId="24" priority="22" operator="equal">
       <formula>"Not Started"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="23" operator="equal">
       <formula>"Pending"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="24" operator="equal">
       <formula>"In Testing"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="25" operator="equal">
       <formula>"Passed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="26" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="27" operator="equal">
       <formula>"Issues Found"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="28" operator="equal">
       <formula>"Blocked - Awaiting Fix"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="29" operator="equal">
       <formula>"N/A (Upcoming)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J152">
-    <cfRule type="cellIs" dxfId="7" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="30" operator="equal">
       <formula>"Not Started"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="31" operator="equal">
       <formula>"Pending"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="32" operator="equal">
       <formula>"In Testing"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="33" operator="equal">
       <formula>"Passed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="34" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="35" operator="equal">
       <formula>"Issues Found"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="36" operator="equal">
       <formula>"Blocked - Awaiting Fix"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="37" operator="equal">
       <formula>"N/A (Upcoming)"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H107">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+      <formula>"Completed"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+      <formula>"Completed - Needs Fix"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
+      <formula>"Ready to Build"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
+      <formula>"In Progress (Partial)"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+      <formula>"Not Started"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
+      <formula>"Upcoming (Dashboard)"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="7" operator="equal">
+      <formula>"Upcoming (Config)"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="8" operator="equal">
+      <formula>"Upcoming (Mobile)"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="9" operator="equal">
+      <formula>"Upcoming"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" sqref="E2:E152">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F2:F152">
+    <dataValidation type="list" allowBlank="1" sqref="F2:F152 H107">
       <formula1>"Completed,Completed - Needs Fix,Ready to Build,In Progress (Partial),Not Started,Upcoming (Dashboard),Upcoming (Config),Upcoming (Mobile),Upcoming"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G2:G152 I2:I152 K2:K152">
+    <dataValidation type="list" allowBlank="1" sqref="K2:K152 I2:I152 G2:G152">
       <formula1>"Karthick,Saranya,Kavin,Sangeetha"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H2:H152 J2:J152">
+    <dataValidation type="list" allowBlank="1" sqref="J2:J152 H2:H106 H108:H152">
       <formula1>"Not Started,Pending,In Testing,Passed,Failed,Issues Found,Blocked - Awaiting Fix,N/A (Upcoming)"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6455,7 +6637,7 @@
       </c>
       <c r="B5" s="17">
         <f>COUNTIF('Screen Status'!F2:F152,"Completed")</f>
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="C5" s="18">
         <f>COUNTIF('Screen Status'!F2:F152,"Completed - Needs Fix")</f>
@@ -6471,7 +6653,7 @@
       </c>
       <c r="F5" s="21">
         <f>COUNTIF('Screen Status'!F2:F152,"Not Started")</f>
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="G5" s="22">
         <f>COUNTIF('Screen Status'!F2:F152,"Upcoming*")</f>
@@ -6577,7 +6759,7 @@
       </c>
       <c r="B10" s="28">
         <f>COUNTIFS('Screen Status'!B2:B152,"Administration",'Screen Status'!F2:F152,"Completed")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" s="28">
         <f>COUNTIFS('Screen Status'!B2:B152,"Administration",'Screen Status'!F2:F152,"Completed - Needs Fix")</f>
@@ -6593,7 +6775,7 @@
       </c>
       <c r="F10" s="28">
         <f>COUNTIFS('Screen Status'!B2:B152,"Administration",'Screen Status'!F2:F152,"Not Started")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G10" s="28">
         <f>COUNTIFS('Screen Status'!B2:B152,"Administration",'Screen Status'!F2:F152,"Upcoming (Dashboard)")</f>
@@ -6712,7 +6894,7 @@
       </c>
       <c r="B13" s="28">
         <f>COUNTIFS('Screen Status'!B2:B152,"Contacts",'Screen Status'!F2:F152,"Completed")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" s="28">
         <f>COUNTIFS('Screen Status'!B2:B152,"Contacts",'Screen Status'!F2:F152,"Completed - Needs Fix")</f>
@@ -6728,7 +6910,7 @@
       </c>
       <c r="F13" s="28">
         <f>COUNTIFS('Screen Status'!B2:B152,"Contacts",'Screen Status'!F2:F152,"Not Started")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" s="28">
         <f>COUNTIFS('Screen Status'!B2:B152,"Contacts",'Screen Status'!F2:F152,"Upcoming (Dashboard)")</f>
@@ -6802,7 +6984,7 @@
       </c>
       <c r="B15" s="28">
         <f>COUNTIFS('Screen Status'!B2:B152,"Fundraising",'Screen Status'!F2:F152,"Completed")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C15" s="28">
         <f>COUNTIFS('Screen Status'!B2:B152,"Fundraising",'Screen Status'!F2:F152,"Completed - Needs Fix")</f>
@@ -6818,7 +7000,7 @@
       </c>
       <c r="F15" s="28">
         <f>COUNTIFS('Screen Status'!B2:B152,"Fundraising",'Screen Status'!F2:F152,"Not Started")</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G15" s="28">
         <f>COUNTIFS('Screen Status'!B2:B152,"Fundraising",'Screen Status'!F2:F152,"Upcoming (Dashboard)")</f>
@@ -7207,7 +7389,7 @@
       </c>
       <c r="B24" s="29">
         <f>COUNTIF('Screen Status'!F2:F152,"Completed")</f>
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="C24" s="29">
         <f>COUNTIF('Screen Status'!F2:F152,"Completed - Needs Fix")</f>
@@ -7223,7 +7405,7 @@
       </c>
       <c r="F24" s="29">
         <f>COUNTIF('Screen Status'!F2:F152,"Not Started")</f>
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="G24" s="29">
         <f>COUNTIF('Screen Status'!F2:F152,"Upcoming (Dashboard)")</f>
@@ -7590,7 +7772,7 @@
       </c>
       <c r="C32" s="28">
         <f>COUNTIFS('Screen Status'!B2:B152,"Contacts",'Screen Status'!H2:H152,"Pending")</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D32" s="28">
         <f>COUNTIFS('Screen Status'!B2:B152,"Contacts",'Screen Status'!H2:H152,"In Testing")</f>
@@ -8349,7 +8531,7 @@
       </c>
       <c r="C43" s="29">
         <f>COUNTIF('Screen Status'!H2:H152,"Pending")</f>
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D43" s="29">
         <f>COUNTIF('Screen Status'!H2:H152,"In Testing")</f>
@@ -8436,7 +8618,7 @@
       </c>
       <c r="B47" s="28">
         <f>COUNTIFS('Screen Status'!E2:E152,"High",'Screen Status'!F2:F152,"Completed")</f>
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C47" s="28">
         <f>COUNTIFS('Screen Status'!E2:E152,"High",'Screen Status'!F2:F152,"In Progress (Partial)")</f>
@@ -8444,7 +8626,7 @@
       </c>
       <c r="D47" s="28">
         <f>COUNTIF('Screen Status'!E2:E152,"High")-COUNTIFS('Screen Status'!E2:E152,"High",'Screen Status'!F2:F152,"Completed")-COUNTIFS('Screen Status'!E2:E152,"High",'Screen Status'!F2:F152,"In Progress (Partial)")</f>
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E47" s="29">
         <f>COUNTIF('Screen Status'!E2:E152,"High")</f>
@@ -8457,7 +8639,7 @@
       </c>
       <c r="B48" s="28">
         <f>COUNTIFS('Screen Status'!E2:E152,"Medium",'Screen Status'!F2:F152,"Completed")</f>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C48" s="28">
         <f>COUNTIFS('Screen Status'!E2:E152,"Medium",'Screen Status'!F2:F152,"In Progress (Partial)")</f>
@@ -8465,7 +8647,7 @@
       </c>
       <c r="D48" s="28">
         <f>COUNTIF('Screen Status'!E2:E152,"Medium")-COUNTIFS('Screen Status'!E2:E152,"Medium",'Screen Status'!F2:F152,"Completed")-COUNTIFS('Screen Status'!E2:E152,"Medium",'Screen Status'!F2:F152,"In Progress (Partial)")</f>
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E48" s="29">
         <f>COUNTIF('Screen Status'!E2:E152,"Medium")</f>
@@ -8539,7 +8721,7 @@
       </c>
       <c r="B53" s="28">
         <f>COUNTIFS('Screen Status'!G2:G152,"Karthick",'Screen Status'!F2:F152,"Completed")+COUNTIFS('Screen Status'!G2:G152,"Karthick",'Screen Status'!F2:F152,"Completed - Needs Fix")</f>
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="C53" s="28">
         <f>COUNTIFS('Screen Status'!I2:I152,"Karthick",'Screen Status'!H2:H152,"Passed")</f>
@@ -8555,7 +8737,7 @@
       </c>
       <c r="F53" s="28">
         <f>COUNTIFS('Screen Status'!I2:I152,"Karthick",'Screen Status'!H2:H152,"Pending")+COUNTIFS('Screen Status'!I2:I152,"Karthick",'Screen Status'!H2:H152,"Not Started")+COUNTIFS('Screen Status'!I2:I152,"Karthick",'Screen Status'!H2:H152,"In Testing")+COUNTIFS('Screen Status'!I2:I152,"Karthick",'Screen Status'!H2:H152,"Blocked - Awaiting Fix")</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G53" s="28">
         <f>COUNTIFS('Screen Status'!K2:K152,"Karthick",'Screen Status'!J2:J152,"Passed")</f>
@@ -8575,7 +8757,7 @@
       </c>
       <c r="K53" s="29">
         <f>SUM(B53:J53)</f>
-        <v>63</v>
+        <v>80</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">

--- a/pss-2.0-global/.claude/screen-tracker/SCREEN-STATUS-OVERVIEW.xlsx
+++ b/pss-2.0-global/.claude/screen-tracker/SCREEN-STATUS-OVERVIEW.xlsx
@@ -768,7 +768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N139"/>
+  <dimension ref="A1:N138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1801,63 +1801,67 @@
     </row>
     <row r="18">
       <c r="A18" s="21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18" s="21" t="inlineStr">
         <is>
-          <t>Fundraising</t>
+          <t>Contacts</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>Fundraising Dashboard</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
         <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="E18" s="29" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F18" s="33" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G18" s="24" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+        <v>1</v>
+      </c>
+      <c r="G18" s="23" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr">
         <is>
-          <t>N/A (Upcoming)</t>
+          <t>Karthick</t>
         </is>
       </c>
       <c r="I18" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="30" t="inlineStr">
-        <is>
-          <t>N/A (Upcoming)</t>
-        </is>
-      </c>
-      <c r="K18" s="21" t="n"/>
+        <v>1.5</v>
+      </c>
+      <c r="J18" s="23" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="K18" s="21" t="inlineStr">
+        <is>
+          <t>Kavin</t>
+        </is>
+      </c>
       <c r="L18" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" s="30" t="inlineStr">
-        <is>
-          <t>N/A (Upcoming)</t>
+        <v>1.5</v>
+      </c>
+      <c r="M18" s="24" t="inlineStr">
+        <is>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="N18" s="21" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19" s="21" t="inlineStr">
         <is>
@@ -1866,12 +1870,12 @@
       </c>
       <c r="C19" s="21" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Contact Type</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
         <is>
-          <t>FLOW</t>
+          <t>MASTER_GRID</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -1880,7 +1884,7 @@
         </is>
       </c>
       <c r="F19" s="33" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G19" s="23" t="inlineStr">
         <is>
@@ -1893,20 +1897,20 @@
         </is>
       </c>
       <c r="I19" s="33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J19" s="23" t="inlineStr">
-        <is>
-          <t>Passed</t>
+        <v>0.75</v>
+      </c>
+      <c r="J19" s="27" t="inlineStr">
+        <is>
+          <t>Blocked - Awaiting Fix</t>
         </is>
       </c>
       <c r="K19" s="21" t="inlineStr">
         <is>
-          <t>Kavin</t>
+          <t>Saranya</t>
         </is>
       </c>
       <c r="L19" s="33" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="M19" s="24" t="inlineStr">
         <is>
@@ -1917,7 +1921,7 @@
     </row>
     <row r="20">
       <c r="A20" s="21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20" s="21" t="inlineStr">
         <is>
@@ -1926,12 +1930,12 @@
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>Contact Type</t>
+          <t>Family</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
         <is>
-          <t>MASTER_GRID</t>
+          <t>FLOW</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -1940,7 +1944,7 @@
         </is>
       </c>
       <c r="F20" s="33" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G20" s="23" t="inlineStr">
         <is>
@@ -1953,11 +1957,11 @@
         </is>
       </c>
       <c r="I20" s="33" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="J20" s="27" t="inlineStr">
-        <is>
-          <t>Blocked - Awaiting Fix</t>
+        <v>1.5</v>
+      </c>
+      <c r="J20" s="26" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="K20" s="21" t="inlineStr">
@@ -1966,7 +1970,7 @@
         </is>
       </c>
       <c r="L20" s="33" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="M20" s="24" t="inlineStr">
         <is>
@@ -1977,7 +1981,7 @@
     </row>
     <row r="21">
       <c r="A21" s="21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" s="21" t="inlineStr">
         <is>
@@ -1986,7 +1990,7 @@
       </c>
       <c r="C21" s="21" t="inlineStr">
         <is>
-          <t>Family</t>
+          <t>Duplicate Detection</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -2022,7 +2026,7 @@
       </c>
       <c r="K21" s="21" t="inlineStr">
         <is>
-          <t>Saranya</t>
+          <t>Karthick</t>
         </is>
       </c>
       <c r="L21" s="33" t="n">
@@ -2037,7 +2041,7 @@
     </row>
     <row r="22">
       <c r="A22" s="21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B22" s="21" t="inlineStr">
         <is>
@@ -2046,21 +2050,21 @@
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>Duplicate Detection</t>
+          <t>Tags &amp; Segmentation</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
         <is>
-          <t>FLOW</t>
-        </is>
-      </c>
-      <c r="E22" s="22" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>MASTER_GRID</t>
+        </is>
+      </c>
+      <c r="E22" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F22" s="33" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="G22" s="23" t="inlineStr">
         <is>
@@ -2073,7 +2077,7 @@
         </is>
       </c>
       <c r="I22" s="33" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J22" s="26" t="inlineStr">
         <is>
@@ -2082,11 +2086,11 @@
       </c>
       <c r="K22" s="21" t="inlineStr">
         <is>
-          <t>Karthick</t>
+          <t>Saranya</t>
         </is>
       </c>
       <c r="L22" s="33" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M22" s="24" t="inlineStr">
         <is>
@@ -2097,7 +2101,7 @@
     </row>
     <row r="23">
       <c r="A23" s="21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B23" s="21" t="inlineStr">
         <is>
@@ -2106,17 +2110,17 @@
       </c>
       <c r="C23" s="21" t="inlineStr">
         <is>
-          <t>Tags &amp; Segmentation</t>
+          <t>Contact Import</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
         <is>
-          <t>MASTER_GRID</t>
-        </is>
-      </c>
-      <c r="E23" s="27" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F23" s="33" t="n">
@@ -2129,20 +2133,20 @@
       </c>
       <c r="H23" s="21" t="inlineStr">
         <is>
-          <t>Karthick</t>
+          <t>Kavin</t>
         </is>
       </c>
       <c r="I23" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="J23" s="26" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="J23" s="23" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="K23" s="21" t="inlineStr">
         <is>
-          <t>Saranya</t>
+          <t>Kavin</t>
         </is>
       </c>
       <c r="L23" s="33" t="n">
@@ -2157,16 +2161,16 @@
     </row>
     <row r="24">
       <c r="A24" s="21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B24" s="21" t="inlineStr">
         <is>
-          <t>Contacts</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
         <is>
-          <t>Contact Import</t>
+          <t>Email Template</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -2189,7 +2193,7 @@
       </c>
       <c r="H24" s="21" t="inlineStr">
         <is>
-          <t>Kavin</t>
+          <t>Karthick</t>
         </is>
       </c>
       <c r="I24" s="33" t="n">
@@ -2202,7 +2206,7 @@
       </c>
       <c r="K24" s="21" t="inlineStr">
         <is>
-          <t>Kavin</t>
+          <t>Saranya</t>
         </is>
       </c>
       <c r="L24" s="33" t="n">
@@ -2217,7 +2221,7 @@
     </row>
     <row r="25">
       <c r="A25" s="21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B25" s="21" t="inlineStr">
         <is>
@@ -2226,7 +2230,7 @@
       </c>
       <c r="C25" s="21" t="inlineStr">
         <is>
-          <t>Email Template</t>
+          <t>Email Campaign/SendJob</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -2240,7 +2244,7 @@
         </is>
       </c>
       <c r="F25" s="33" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G25" s="23" t="inlineStr">
         <is>
@@ -2249,24 +2253,20 @@
       </c>
       <c r="H25" s="21" t="inlineStr">
         <is>
-          <t>Karthick</t>
+          <t>Saranya</t>
         </is>
       </c>
       <c r="I25" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="23" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="K25" s="21" t="inlineStr">
-        <is>
-          <t>Saranya</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="J25" s="24" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K25" s="21" t="n"/>
       <c r="L25" s="33" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M25" s="24" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
     </row>
     <row r="26">
       <c r="A26" s="21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B26" s="21" t="inlineStr">
         <is>
@@ -2286,12 +2286,12 @@
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>Email Campaign/SendJob</t>
+          <t>Placeholder Definition</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
         <is>
-          <t>FLOW</t>
+          <t>MASTER_GRID</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="F26" s="33" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G26" s="23" t="inlineStr">
         <is>
@@ -2309,20 +2309,24 @@
       </c>
       <c r="H26" s="21" t="inlineStr">
         <is>
+          <t>Karthick</t>
+        </is>
+      </c>
+      <c r="I26" s="33" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J26" s="26" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K26" s="21" t="inlineStr">
+        <is>
           <t>Saranya</t>
         </is>
       </c>
-      <c r="I26" s="33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J26" s="24" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K26" s="21" t="n"/>
       <c r="L26" s="33" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="M26" s="24" t="inlineStr">
         <is>
@@ -2333,7 +2337,7 @@
     </row>
     <row r="27">
       <c r="A27" s="21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B27" s="21" t="inlineStr">
         <is>
@@ -2342,12 +2346,12 @@
       </c>
       <c r="C27" s="21" t="inlineStr">
         <is>
-          <t>Placeholder Definition</t>
+          <t>Saved Filter</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
         <is>
-          <t>MASTER_GRID</t>
+          <t>FLOW</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -2356,7 +2360,7 @@
         </is>
       </c>
       <c r="F27" s="33" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G27" s="23" t="inlineStr">
         <is>
@@ -2369,11 +2373,11 @@
         </is>
       </c>
       <c r="I27" s="33" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="J27" s="26" t="inlineStr">
-        <is>
-          <t>Pending</t>
+        <v>1</v>
+      </c>
+      <c r="J27" s="23" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="K27" s="21" t="inlineStr">
@@ -2382,7 +2386,7 @@
         </is>
       </c>
       <c r="L27" s="33" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="M27" s="24" t="inlineStr">
         <is>
@@ -2393,7 +2397,7 @@
     </row>
     <row r="28">
       <c r="A28" s="21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B28" s="21" t="inlineStr">
         <is>
@@ -2402,7 +2406,7 @@
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>Saved Filter</t>
+          <t>Company Email Provider</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -2431,14 +2435,14 @@
       <c r="I28" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="J28" s="23" t="inlineStr">
-        <is>
-          <t>Passed</t>
+      <c r="J28" s="26" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="K28" s="21" t="inlineStr">
         <is>
-          <t>Saranya</t>
+          <t>Karthick</t>
         </is>
       </c>
       <c r="L28" s="33" t="n">
@@ -2453,7 +2457,7 @@
     </row>
     <row r="29">
       <c r="A29" s="21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B29" s="21" t="inlineStr">
         <is>
@@ -2462,7 +2466,7 @@
       </c>
       <c r="C29" s="21" t="inlineStr">
         <is>
-          <t>Company Email Provider</t>
+          <t>SMS Template</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
@@ -2470,9 +2474,9 @@
           <t>FLOW</t>
         </is>
       </c>
-      <c r="E29" s="22" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="E29" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F29" s="33" t="n">
@@ -2498,7 +2502,7 @@
       </c>
       <c r="K29" s="21" t="inlineStr">
         <is>
-          <t>Karthick</t>
+          <t>Saranya</t>
         </is>
       </c>
       <c r="L29" s="33" t="n">
@@ -2513,7 +2517,7 @@
     </row>
     <row r="30">
       <c r="A30" s="21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B30" s="21" t="inlineStr">
         <is>
@@ -2522,7 +2526,7 @@
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>SMS Template</t>
+          <t>SMS Campaign</t>
         </is>
       </c>
       <c r="D30" s="21" t="inlineStr">
@@ -2530,13 +2534,13 @@
           <t>FLOW</t>
         </is>
       </c>
-      <c r="E30" s="27" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F30" s="33" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G30" s="23" t="inlineStr">
         <is>
@@ -2549,7 +2553,7 @@
         </is>
       </c>
       <c r="I30" s="33" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J30" s="26" t="inlineStr">
         <is>
@@ -2562,7 +2566,7 @@
         </is>
       </c>
       <c r="L30" s="33" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M30" s="24" t="inlineStr">
         <is>
@@ -2573,7 +2577,7 @@
     </row>
     <row r="31">
       <c r="A31" s="21" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B31" s="21" t="inlineStr">
         <is>
@@ -2582,7 +2586,7 @@
       </c>
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>SMS Campaign</t>
+          <t>WhatsApp Template</t>
         </is>
       </c>
       <c r="D31" s="21" t="inlineStr">
@@ -2590,13 +2594,13 @@
           <t>FLOW</t>
         </is>
       </c>
-      <c r="E31" s="22" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="E31" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F31" s="33" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="G31" s="23" t="inlineStr">
         <is>
@@ -2609,7 +2613,7 @@
         </is>
       </c>
       <c r="I31" s="33" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J31" s="26" t="inlineStr">
         <is>
@@ -2618,11 +2622,11 @@
       </c>
       <c r="K31" s="21" t="inlineStr">
         <is>
-          <t>Saranya</t>
+          <t>Karthick</t>
         </is>
       </c>
       <c r="L31" s="33" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M31" s="24" t="inlineStr">
         <is>
@@ -2633,7 +2637,7 @@
     </row>
     <row r="32">
       <c r="A32" s="21" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B32" s="21" t="inlineStr">
         <is>
@@ -2642,7 +2646,7 @@
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>WhatsApp Template</t>
+          <t>WhatsApp Campaign</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr">
@@ -2650,13 +2654,13 @@
           <t>FLOW</t>
         </is>
       </c>
-      <c r="E32" s="27" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F32" s="33" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G32" s="23" t="inlineStr">
         <is>
@@ -2665,24 +2669,24 @@
       </c>
       <c r="H32" s="21" t="inlineStr">
         <is>
-          <t>Karthick</t>
+          <t>Kavin</t>
         </is>
       </c>
       <c r="I32" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" s="26" t="inlineStr">
-        <is>
-          <t>Pending</t>
+        <v>1.5</v>
+      </c>
+      <c r="J32" s="24" t="inlineStr">
+        <is>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="K32" s="21" t="inlineStr">
         <is>
-          <t>Karthick</t>
+          <t>Kavin</t>
         </is>
       </c>
       <c r="L32" s="33" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M32" s="24" t="inlineStr">
         <is>
@@ -2693,7 +2697,7 @@
     </row>
     <row r="33">
       <c r="A33" s="21" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B33" s="21" t="inlineStr">
         <is>
@@ -2702,7 +2706,7 @@
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>WhatsApp Campaign</t>
+          <t>WhatsApp Conversations</t>
         </is>
       </c>
       <c r="D33" s="21" t="inlineStr">
@@ -2718,14 +2722,14 @@
       <c r="F33" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="G33" s="23" t="inlineStr">
-        <is>
-          <t>Completed</t>
+      <c r="G33" s="24" t="inlineStr">
+        <is>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="H33" s="21" t="inlineStr">
         <is>
-          <t>Kavin</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="I33" s="33" t="n">
@@ -2753,7 +2757,7 @@
     </row>
     <row r="34">
       <c r="A34" s="21" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B34" s="21" t="inlineStr">
         <is>
@@ -2762,34 +2766,34 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>WhatsApp Conversations</t>
+          <t>WhatsApp Setup</t>
         </is>
       </c>
       <c r="D34" s="21" t="inlineStr">
         <is>
-          <t>FLOW</t>
-        </is>
-      </c>
-      <c r="E34" s="22" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="E34" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F34" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" s="24" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+        <v>0.75</v>
+      </c>
+      <c r="G34" s="23" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
       <c r="H34" s="21" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Kavin</t>
         </is>
       </c>
       <c r="I34" s="33" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J34" s="24" t="inlineStr">
         <is>
@@ -2802,7 +2806,7 @@
         </is>
       </c>
       <c r="L34" s="33" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M34" s="24" t="inlineStr">
         <is>
@@ -2813,7 +2817,7 @@
     </row>
     <row r="35">
       <c r="A35" s="21" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B35" s="21" t="inlineStr">
         <is>
@@ -2822,17 +2826,17 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>WhatsApp Setup</t>
+          <t>Notification Center</t>
         </is>
       </c>
       <c r="D35" s="21" t="inlineStr">
         <is>
-          <t>Config</t>
-        </is>
-      </c>
-      <c r="E35" s="27" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="E35" s="22" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F35" s="33" t="n">
@@ -2845,15 +2849,15 @@
       </c>
       <c r="H35" s="21" t="inlineStr">
         <is>
-          <t>Kavin</t>
+          <t>Karthick</t>
         </is>
       </c>
       <c r="I35" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="J35" s="24" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J35" s="23" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="K35" s="21" t="inlineStr">
@@ -2873,7 +2877,7 @@
     </row>
     <row r="36">
       <c r="A36" s="21" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B36" s="21" t="inlineStr">
         <is>
@@ -2882,7 +2886,7 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>Notification Center</t>
+          <t>Notification Templates</t>
         </is>
       </c>
       <c r="D36" s="21" t="inlineStr">
@@ -2890,9 +2894,9 @@
           <t>FLOW</t>
         </is>
       </c>
-      <c r="E36" s="22" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="E36" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F36" s="33" t="n">
@@ -2933,7 +2937,7 @@
     </row>
     <row r="37">
       <c r="A37" s="21" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B37" s="21" t="inlineStr">
         <is>
@@ -2942,7 +2946,7 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>Notification Templates</t>
+          <t>Automation Workflow</t>
         </is>
       </c>
       <c r="D37" s="21" t="inlineStr">
@@ -2950,39 +2954,35 @@
           <t>FLOW</t>
         </is>
       </c>
-      <c r="E37" s="27" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="E37" s="29" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="F37" s="33" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G37" s="23" t="inlineStr">
-        <is>
-          <t>Completed</t>
+        <v>1</v>
+      </c>
+      <c r="G37" s="24" t="inlineStr">
+        <is>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="H37" s="21" t="inlineStr">
         <is>
-          <t>Karthick</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="I37" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" s="23" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="K37" s="21" t="inlineStr">
-        <is>
-          <t>Kavin</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="J37" s="24" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K37" s="21" t="n"/>
       <c r="L37" s="33" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M37" s="24" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
     </row>
     <row r="38">
       <c r="A38" s="21" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B38" s="21" t="inlineStr">
         <is>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>Automation Workflow</t>
+          <t>Email Analytics</t>
         </is>
       </c>
       <c r="D38" s="21" t="inlineStr">
         <is>
-          <t>FLOW</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="E38" s="29" t="inlineStr">
@@ -3016,59 +3016,59 @@
         </is>
       </c>
       <c r="F38" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="24" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+        <v>0.75</v>
+      </c>
+      <c r="G38" s="23" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
       <c r="H38" s="21" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Karthick</t>
         </is>
       </c>
       <c r="I38" s="33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J38" s="24" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+        <v>1</v>
+      </c>
+      <c r="J38" s="30" t="inlineStr">
+        <is>
+          <t>N/A (Upcoming)</t>
         </is>
       </c>
       <c r="K38" s="21" t="n"/>
       <c r="L38" s="33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M38" s="24" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+        <v>1</v>
+      </c>
+      <c r="M38" s="30" t="inlineStr">
+        <is>
+          <t>N/A (Upcoming)</t>
         </is>
       </c>
       <c r="N38" s="21" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="21" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B39" s="21" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Organization</t>
         </is>
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>Email Analytics</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="D39" s="21" t="inlineStr">
         <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="E39" s="29" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="E39" s="22" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F39" s="33" t="n">
@@ -3087,25 +3087,29 @@
       <c r="I39" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="J39" s="30" t="inlineStr">
-        <is>
-          <t>N/A (Upcoming)</t>
-        </is>
-      </c>
-      <c r="K39" s="21" t="n"/>
+      <c r="J39" s="23" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="K39" s="21" t="inlineStr">
+        <is>
+          <t>Kavin</t>
+        </is>
+      </c>
       <c r="L39" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="M39" s="30" t="inlineStr">
-        <is>
-          <t>N/A (Upcoming)</t>
+      <c r="M39" s="24" t="inlineStr">
+        <is>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="N39" s="21" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="21" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B40" s="21" t="inlineStr">
         <is>
@@ -3114,7 +3118,7 @@
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="D40" s="21" t="inlineStr">
@@ -3128,7 +3132,7 @@
         </is>
       </c>
       <c r="F40" s="33" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G40" s="23" t="inlineStr">
         <is>
@@ -3141,7 +3145,7 @@
         </is>
       </c>
       <c r="I40" s="33" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J40" s="23" t="inlineStr">
         <is>
@@ -3154,7 +3158,7 @@
         </is>
       </c>
       <c r="L40" s="33" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M40" s="24" t="inlineStr">
         <is>
@@ -3165,7 +3169,7 @@
     </row>
     <row r="41">
       <c r="A41" s="21" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B41" s="21" t="inlineStr">
         <is>
@@ -3174,12 +3178,12 @@
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Branch</t>
         </is>
       </c>
       <c r="D41" s="21" t="inlineStr">
         <is>
-          <t>FLOW</t>
+          <t>MASTER_GRID</t>
         </is>
       </c>
       <c r="E41" s="22" t="inlineStr">
@@ -3188,7 +3192,7 @@
         </is>
       </c>
       <c r="F41" s="33" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G41" s="23" t="inlineStr">
         <is>
@@ -3201,7 +3205,7 @@
         </is>
       </c>
       <c r="I41" s="33" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="J41" s="23" t="inlineStr">
         <is>
@@ -3214,7 +3218,7 @@
         </is>
       </c>
       <c r="L41" s="33" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="M41" s="24" t="inlineStr">
         <is>
@@ -3225,7 +3229,7 @@
     </row>
     <row r="42">
       <c r="A42" s="21" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B42" s="21" t="inlineStr">
         <is>
@@ -3234,12 +3238,12 @@
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>Branch</t>
+          <t>Staff (combined: Staff + User Role)</t>
         </is>
       </c>
       <c r="D42" s="21" t="inlineStr">
         <is>
-          <t>MASTER_GRID</t>
+          <t>FLOW</t>
         </is>
       </c>
       <c r="E42" s="22" t="inlineStr">
@@ -3248,33 +3252,29 @@
         </is>
       </c>
       <c r="F42" s="33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G42" s="23" t="inlineStr">
-        <is>
-          <t>Completed</t>
+        <v>1</v>
+      </c>
+      <c r="G42" s="28" t="inlineStr">
+        <is>
+          <t>In Progress (Partial)</t>
         </is>
       </c>
       <c r="H42" s="21" t="inlineStr">
         <is>
-          <t>Karthick</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="I42" s="33" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="J42" s="23" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="K42" s="21" t="inlineStr">
-        <is>
-          <t>Kavin</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="J42" s="24" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K42" s="21" t="n"/>
       <c r="L42" s="33" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="M42" s="24" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
     </row>
     <row r="43">
       <c r="A43" s="21" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B43" s="21" t="inlineStr">
         <is>
@@ -3294,12 +3294,12 @@
       </c>
       <c r="C43" s="21" t="inlineStr">
         <is>
-          <t>Staff (combined: Staff + User Role)</t>
+          <t>Staff Category</t>
         </is>
       </c>
       <c r="D43" s="21" t="inlineStr">
         <is>
-          <t>FLOW</t>
+          <t>MASTER_GRID</t>
         </is>
       </c>
       <c r="E43" s="22" t="inlineStr">
@@ -3308,29 +3308,33 @@
         </is>
       </c>
       <c r="F43" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" s="28" t="inlineStr">
-        <is>
-          <t>In Progress (Partial)</t>
+        <v>0.5</v>
+      </c>
+      <c r="G43" s="23" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
       <c r="H43" s="21" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Karthick</t>
         </is>
       </c>
       <c r="I43" s="33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J43" s="24" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K43" s="21" t="n"/>
+        <v>0.75</v>
+      </c>
+      <c r="J43" s="26" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K43" s="21" t="inlineStr">
+        <is>
+          <t>Saranya</t>
+        </is>
+      </c>
       <c r="L43" s="33" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="M43" s="24" t="inlineStr">
         <is>
@@ -3341,7 +3345,7 @@
     </row>
     <row r="44">
       <c r="A44" s="21" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B44" s="21" t="inlineStr">
         <is>
@@ -3350,12 +3354,12 @@
       </c>
       <c r="C44" s="21" t="inlineStr">
         <is>
-          <t>Staff Category</t>
+          <t>Organizational Unit</t>
         </is>
       </c>
       <c r="D44" s="21" t="inlineStr">
         <is>
-          <t>MASTER_GRID</t>
+          <t>FLOW</t>
         </is>
       </c>
       <c r="E44" s="22" t="inlineStr">
@@ -3364,7 +3368,7 @@
         </is>
       </c>
       <c r="F44" s="33" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G44" s="23" t="inlineStr">
         <is>
@@ -3377,20 +3381,20 @@
         </is>
       </c>
       <c r="I44" s="33" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="J44" s="26" t="inlineStr">
-        <is>
-          <t>Pending</t>
+        <v>1</v>
+      </c>
+      <c r="J44" s="23" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="K44" s="21" t="inlineStr">
         <is>
-          <t>Saranya</t>
+          <t>Kavin</t>
         </is>
       </c>
       <c r="L44" s="33" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="M44" s="24" t="inlineStr">
         <is>
@@ -3401,7 +3405,7 @@
     </row>
     <row r="45">
       <c r="A45" s="21" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B45" s="21" t="inlineStr">
         <is>
@@ -3410,7 +3414,7 @@
       </c>
       <c r="C45" s="21" t="inlineStr">
         <is>
-          <t>Organizational Unit</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="D45" s="21" t="inlineStr">
@@ -3426,29 +3430,25 @@
       <c r="F45" s="33" t="n">
         <v>0.75</v>
       </c>
-      <c r="G45" s="23" t="inlineStr">
-        <is>
-          <t>Completed</t>
+      <c r="G45" s="24" t="inlineStr">
+        <is>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="H45" s="21" t="inlineStr">
         <is>
-          <t>Karthick</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="I45" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="J45" s="23" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="K45" s="21" t="inlineStr">
-        <is>
-          <t>Kavin</t>
-        </is>
-      </c>
+      <c r="J45" s="24" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K45" s="21" t="n"/>
       <c r="L45" s="33" t="n">
         <v>1</v>
       </c>
@@ -3461,7 +3461,7 @@
     </row>
     <row r="46">
       <c r="A46" s="21" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B46" s="21" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="C46" s="21" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>Event Ticketing</t>
         </is>
       </c>
       <c r="D46" s="21" t="inlineStr">
@@ -3484,29 +3484,33 @@
         </is>
       </c>
       <c r="F46" s="33" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G46" s="24" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+        <v>1</v>
+      </c>
+      <c r="G46" s="23" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
       <c r="H46" s="21" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Karthick</t>
         </is>
       </c>
       <c r="I46" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J46" s="24" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K46" s="21" t="n"/>
+        <v>1.5</v>
+      </c>
+      <c r="J46" s="26" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K46" s="21" t="inlineStr">
+        <is>
+          <t>Karthick</t>
+        </is>
+      </c>
       <c r="L46" s="33" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M46" s="24" t="inlineStr">
         <is>
@@ -3517,7 +3521,7 @@
     </row>
     <row r="47">
       <c r="A47" s="21" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B47" s="21" t="inlineStr">
         <is>
@@ -3526,21 +3530,21 @@
       </c>
       <c r="C47" s="21" t="inlineStr">
         <is>
-          <t>Event Ticketing</t>
+          <t>Event Analytics</t>
         </is>
       </c>
       <c r="D47" s="21" t="inlineStr">
         <is>
-          <t>FLOW</t>
-        </is>
-      </c>
-      <c r="E47" s="22" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="E47" s="29" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="F47" s="33" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="G47" s="23" t="inlineStr">
         <is>
@@ -3553,31 +3557,27 @@
         </is>
       </c>
       <c r="I47" s="33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J47" s="26" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="K47" s="21" t="inlineStr">
-        <is>
-          <t>Karthick</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J47" s="30" t="inlineStr">
+        <is>
+          <t>N/A (Upcoming)</t>
+        </is>
+      </c>
+      <c r="K47" s="21" t="n"/>
       <c r="L47" s="33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M47" s="24" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+        <v>1</v>
+      </c>
+      <c r="M47" s="30" t="inlineStr">
+        <is>
+          <t>N/A (Upcoming)</t>
         </is>
       </c>
       <c r="N47" s="21" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="21" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B48" s="21" t="inlineStr">
         <is>
@@ -3586,21 +3586,21 @@
       </c>
       <c r="C48" s="21" t="inlineStr">
         <is>
-          <t>Event Analytics</t>
+          <t>Auction Management</t>
         </is>
       </c>
       <c r="D48" s="21" t="inlineStr">
         <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="E48" s="29" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="E48" s="22" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F48" s="33" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G48" s="23" t="inlineStr">
         <is>
@@ -3613,36 +3613,40 @@
         </is>
       </c>
       <c r="I48" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" s="30" t="inlineStr">
-        <is>
-          <t>N/A (Upcoming)</t>
-        </is>
-      </c>
-      <c r="K48" s="21" t="n"/>
+        <v>1.5</v>
+      </c>
+      <c r="J48" s="31" t="inlineStr">
+        <is>
+          <t>In Testing</t>
+        </is>
+      </c>
+      <c r="K48" s="21" t="inlineStr">
+        <is>
+          <t>Karthick</t>
+        </is>
+      </c>
       <c r="L48" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="M48" s="30" t="inlineStr">
-        <is>
-          <t>N/A (Upcoming)</t>
+        <v>1.5</v>
+      </c>
+      <c r="M48" s="24" t="inlineStr">
+        <is>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="N48" s="21" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="21" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B49" s="21" t="inlineStr">
         <is>
-          <t>Organization</t>
+          <t>Case Management</t>
         </is>
       </c>
       <c r="C49" s="21" t="inlineStr">
         <is>
-          <t>Auction Management</t>
+          <t>Beneficiary</t>
         </is>
       </c>
       <c r="D49" s="21" t="inlineStr">
@@ -3650,9 +3654,9 @@
           <t>FLOW</t>
         </is>
       </c>
-      <c r="E49" s="22" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="E49" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F49" s="33" t="n">
@@ -3671,14 +3675,14 @@
       <c r="I49" s="33" t="n">
         <v>1.5</v>
       </c>
-      <c r="J49" s="31" t="inlineStr">
-        <is>
-          <t>In Testing</t>
+      <c r="J49" s="26" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
       <c r="K49" s="21" t="inlineStr">
         <is>
-          <t>Karthick</t>
+          <t>Saranya</t>
         </is>
       </c>
       <c r="L49" s="33" t="n">
@@ -3693,7 +3697,7 @@
     </row>
     <row r="50">
       <c r="A50" s="21" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B50" s="21" t="inlineStr">
         <is>
@@ -3702,7 +3706,7 @@
       </c>
       <c r="C50" s="21" t="inlineStr">
         <is>
-          <t>Beneficiary</t>
+          <t>Case</t>
         </is>
       </c>
       <c r="D50" s="21" t="inlineStr">
@@ -3710,9 +3714,9 @@
           <t>FLOW</t>
         </is>
       </c>
-      <c r="E50" s="27" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="E50" s="22" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F50" s="33" t="n">
@@ -3738,7 +3742,7 @@
       </c>
       <c r="K50" s="21" t="inlineStr">
         <is>
-          <t>Saranya</t>
+          <t>Karthick</t>
         </is>
       </c>
       <c r="L50" s="33" t="n">
@@ -3753,7 +3757,7 @@
     </row>
     <row r="51">
       <c r="A51" s="21" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B51" s="21" t="inlineStr">
         <is>
@@ -3762,21 +3766,21 @@
       </c>
       <c r="C51" s="21" t="inlineStr">
         <is>
-          <t>Case</t>
+          <t>Program</t>
         </is>
       </c>
       <c r="D51" s="21" t="inlineStr">
         <is>
-          <t>FLOW</t>
-        </is>
-      </c>
-      <c r="E51" s="22" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>MASTER_GRID</t>
+        </is>
+      </c>
+      <c r="E51" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F51" s="33" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="G51" s="23" t="inlineStr">
         <is>
@@ -3789,7 +3793,7 @@
         </is>
       </c>
       <c r="I51" s="33" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J51" s="26" t="inlineStr">
         <is>
@@ -3802,7 +3806,7 @@
         </is>
       </c>
       <c r="L51" s="33" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M51" s="24" t="inlineStr">
         <is>
@@ -3813,7 +3817,7 @@
     </row>
     <row r="52">
       <c r="A52" s="21" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B52" s="21" t="inlineStr">
         <is>
@@ -3822,17 +3826,17 @@
       </c>
       <c r="C52" s="21" t="inlineStr">
         <is>
-          <t>Program</t>
+          <t>Case Dashboard</t>
         </is>
       </c>
       <c r="D52" s="21" t="inlineStr">
         <is>
-          <t>MASTER_GRID</t>
-        </is>
-      </c>
-      <c r="E52" s="27" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="E52" s="29" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="F52" s="33" t="n">
@@ -3851,52 +3855,48 @@
       <c r="I52" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="J52" s="26" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="K52" s="21" t="inlineStr">
-        <is>
-          <t>Karthick</t>
-        </is>
-      </c>
+      <c r="J52" s="30" t="inlineStr">
+        <is>
+          <t>N/A (Upcoming)</t>
+        </is>
+      </c>
+      <c r="K52" s="21" t="n"/>
       <c r="L52" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="M52" s="24" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="M52" s="30" t="inlineStr">
+        <is>
+          <t>N/A (Upcoming)</t>
         </is>
       </c>
       <c r="N52" s="21" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="21" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B53" s="21" t="inlineStr">
         <is>
-          <t>Case Management</t>
+          <t>Volunteer</t>
         </is>
       </c>
       <c r="C53" s="21" t="inlineStr">
         <is>
-          <t>Case Dashboard</t>
+          <t>Volunteer</t>
         </is>
       </c>
       <c r="D53" s="21" t="inlineStr">
         <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="E53" s="29" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="E53" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F53" s="33" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G53" s="23" t="inlineStr">
         <is>
@@ -3909,27 +3909,31 @@
         </is>
       </c>
       <c r="I53" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" s="30" t="inlineStr">
-        <is>
-          <t>N/A (Upcoming)</t>
-        </is>
-      </c>
-      <c r="K53" s="21" t="n"/>
+        <v>1.5</v>
+      </c>
+      <c r="J53" s="23" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="K53" s="21" t="inlineStr">
+        <is>
+          <t>Kavin</t>
+        </is>
+      </c>
       <c r="L53" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="M53" s="30" t="inlineStr">
-        <is>
-          <t>N/A (Upcoming)</t>
+        <v>1.5</v>
+      </c>
+      <c r="M53" s="24" t="inlineStr">
+        <is>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="N53" s="21" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="21" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B54" s="21" t="inlineStr">
         <is>
@@ -3938,7 +3942,7 @@
       </c>
       <c r="C54" s="21" t="inlineStr">
         <is>
-          <t>Volunteer</t>
+          <t>Volunteer Schedule</t>
         </is>
       </c>
       <c r="D54" s="21" t="inlineStr">
@@ -3946,13 +3950,13 @@
           <t>FLOW</t>
         </is>
       </c>
-      <c r="E54" s="27" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="E54" s="22" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F54" s="33" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="G54" s="23" t="inlineStr">
         <is>
@@ -3965,7 +3969,7 @@
         </is>
       </c>
       <c r="I54" s="33" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J54" s="23" t="inlineStr">
         <is>
@@ -3978,7 +3982,7 @@
         </is>
       </c>
       <c r="L54" s="33" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M54" s="24" t="inlineStr">
         <is>
@@ -3989,7 +3993,7 @@
     </row>
     <row r="55">
       <c r="A55" s="21" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B55" s="21" t="inlineStr">
         <is>
@@ -3998,7 +4002,7 @@
       </c>
       <c r="C55" s="21" t="inlineStr">
         <is>
-          <t>Volunteer Schedule</t>
+          <t>Hour Tracking</t>
         </is>
       </c>
       <c r="D55" s="21" t="inlineStr">
@@ -4049,7 +4053,7 @@
     </row>
     <row r="56">
       <c r="A56" s="21" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B56" s="21" t="inlineStr">
         <is>
@@ -4058,17 +4062,17 @@
       </c>
       <c r="C56" s="21" t="inlineStr">
         <is>
-          <t>Hour Tracking</t>
+          <t>Volunteer Dashboard</t>
         </is>
       </c>
       <c r="D56" s="21" t="inlineStr">
         <is>
-          <t>FLOW</t>
-        </is>
-      </c>
-      <c r="E56" s="22" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="E56" s="29" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="F56" s="33" t="n">
@@ -4087,85 +4091,85 @@
       <c r="I56" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="J56" s="23" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="K56" s="21" t="inlineStr">
-        <is>
-          <t>Kavin</t>
-        </is>
-      </c>
+      <c r="J56" s="30" t="inlineStr">
+        <is>
+          <t>N/A (Upcoming)</t>
+        </is>
+      </c>
+      <c r="K56" s="21" t="n"/>
       <c r="L56" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="M56" s="24" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="M56" s="30" t="inlineStr">
+        <is>
+          <t>N/A (Upcoming)</t>
         </is>
       </c>
       <c r="N56" s="21" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="21" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B57" s="21" t="inlineStr">
         <is>
-          <t>Volunteer</t>
+          <t>Membership</t>
         </is>
       </c>
       <c r="C57" s="21" t="inlineStr">
         <is>
-          <t>Volunteer Dashboard</t>
+          <t>Membership Tier</t>
         </is>
       </c>
       <c r="D57" s="21" t="inlineStr">
         <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="E57" s="29" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>MASTER_GRID</t>
+        </is>
+      </c>
+      <c r="E57" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F57" s="33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G57" s="23" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H57" s="21" t="inlineStr">
+        <is>
+          <t>Karthick</t>
+        </is>
+      </c>
+      <c r="I57" s="33" t="n">
         <v>0.75</v>
       </c>
-      <c r="G57" s="23" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="H57" s="21" t="inlineStr">
-        <is>
-          <t>Karthick</t>
-        </is>
-      </c>
-      <c r="I57" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J57" s="30" t="inlineStr">
-        <is>
-          <t>N/A (Upcoming)</t>
-        </is>
-      </c>
-      <c r="K57" s="21" t="n"/>
+      <c r="J57" s="26" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K57" s="21" t="inlineStr">
+        <is>
+          <t>Saranya</t>
+        </is>
+      </c>
       <c r="L57" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="M57" s="30" t="inlineStr">
-        <is>
-          <t>N/A (Upcoming)</t>
+        <v>0.75</v>
+      </c>
+      <c r="M57" s="24" t="inlineStr">
+        <is>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="N57" s="21" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="21" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B58" s="21" t="inlineStr">
         <is>
@@ -4174,12 +4178,12 @@
       </c>
       <c r="C58" s="21" t="inlineStr">
         <is>
-          <t>Membership Tier</t>
+          <t>Member Enrollment</t>
         </is>
       </c>
       <c r="D58" s="21" t="inlineStr">
         <is>
-          <t>MASTER_GRID</t>
+          <t>FLOW</t>
         </is>
       </c>
       <c r="E58" s="27" t="inlineStr">
@@ -4188,7 +4192,7 @@
         </is>
       </c>
       <c r="F58" s="33" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G58" s="23" t="inlineStr">
         <is>
@@ -4201,7 +4205,7 @@
         </is>
       </c>
       <c r="I58" s="33" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="J58" s="26" t="inlineStr">
         <is>
@@ -4214,7 +4218,7 @@
         </is>
       </c>
       <c r="L58" s="33" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="M58" s="24" t="inlineStr">
         <is>
@@ -4225,7 +4229,7 @@
     </row>
     <row r="59">
       <c r="A59" s="21" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B59" s="21" t="inlineStr">
         <is>
@@ -4234,21 +4238,21 @@
       </c>
       <c r="C59" s="21" t="inlineStr">
         <is>
-          <t>Member Enrollment</t>
+          <t>Membership Renewal</t>
         </is>
       </c>
       <c r="D59" s="21" t="inlineStr">
         <is>
-          <t>FLOW</t>
-        </is>
-      </c>
-      <c r="E59" s="27" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>MASTER_GRID</t>
+        </is>
+      </c>
+      <c r="E59" s="22" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F59" s="33" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="G59" s="23" t="inlineStr">
         <is>
@@ -4261,7 +4265,7 @@
         </is>
       </c>
       <c r="I59" s="33" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J59" s="26" t="inlineStr">
         <is>
@@ -4274,7 +4278,7 @@
         </is>
       </c>
       <c r="L59" s="33" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M59" s="24" t="inlineStr">
         <is>
@@ -4285,7 +4289,7 @@
     </row>
     <row r="60">
       <c r="A60" s="21" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B60" s="21" t="inlineStr">
         <is>
@@ -4294,21 +4298,21 @@
       </c>
       <c r="C60" s="21" t="inlineStr">
         <is>
-          <t>Membership Renewal</t>
+          <t>Member Portal</t>
         </is>
       </c>
       <c r="D60" s="21" t="inlineStr">
         <is>
-          <t>MASTER_GRID</t>
-        </is>
-      </c>
-      <c r="E60" s="22" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="E60" s="29" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="F60" s="33" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G60" s="23" t="inlineStr">
         <is>
@@ -4323,38 +4327,34 @@
       <c r="I60" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="J60" s="26" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="K60" s="21" t="inlineStr">
-        <is>
-          <t>Saranya</t>
-        </is>
-      </c>
+      <c r="J60" s="30" t="inlineStr">
+        <is>
+          <t>N/A (Upcoming)</t>
+        </is>
+      </c>
+      <c r="K60" s="21" t="n"/>
       <c r="L60" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="M60" s="24" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="M60" s="30" t="inlineStr">
+        <is>
+          <t>N/A (Upcoming)</t>
         </is>
       </c>
       <c r="N60" s="21" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="21" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B61" s="21" t="inlineStr">
         <is>
-          <t>Membership</t>
+          <t>Grants</t>
         </is>
       </c>
       <c r="C61" s="21" t="inlineStr">
         <is>
-          <t>Member Portal</t>
+          <t>Grant</t>
         </is>
       </c>
       <c r="D61" s="21" t="inlineStr">
@@ -4362,9 +4362,9 @@
           <t>FLOW</t>
         </is>
       </c>
-      <c r="E61" s="29" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="E61" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F61" s="33" t="n">
@@ -4381,27 +4381,31 @@
         </is>
       </c>
       <c r="I61" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J61" s="30" t="inlineStr">
-        <is>
-          <t>N/A (Upcoming)</t>
-        </is>
-      </c>
-      <c r="K61" s="21" t="n"/>
+        <v>1.5</v>
+      </c>
+      <c r="J61" s="26" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K61" s="21" t="inlineStr">
+        <is>
+          <t>Karthick</t>
+        </is>
+      </c>
       <c r="L61" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="M61" s="30" t="inlineStr">
-        <is>
-          <t>N/A (Upcoming)</t>
+        <v>1.5</v>
+      </c>
+      <c r="M61" s="24" t="inlineStr">
+        <is>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="N61" s="21" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="21" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B62" s="21" t="inlineStr">
         <is>
@@ -4410,7 +4414,7 @@
       </c>
       <c r="C62" s="21" t="inlineStr">
         <is>
-          <t>Grant</t>
+          <t>Grant Report</t>
         </is>
       </c>
       <c r="D62" s="21" t="inlineStr">
@@ -4418,9 +4422,9 @@
           <t>FLOW</t>
         </is>
       </c>
-      <c r="E62" s="27" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="E62" s="22" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F62" s="33" t="n">
@@ -4461,7 +4465,7 @@
     </row>
     <row r="63">
       <c r="A63" s="21" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B63" s="21" t="inlineStr">
         <is>
@@ -4470,25 +4474,25 @@
       </c>
       <c r="C63" s="21" t="inlineStr">
         <is>
-          <t>Grant Report</t>
+          <t>Grant Calendar</t>
         </is>
       </c>
       <c r="D63" s="21" t="inlineStr">
         <is>
-          <t>FLOW</t>
-        </is>
-      </c>
-      <c r="E63" s="22" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="E63" s="29" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="F63" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="G63" s="23" t="inlineStr">
-        <is>
-          <t>Completed</t>
+        <v>0.75</v>
+      </c>
+      <c r="G63" s="28" t="inlineStr">
+        <is>
+          <t>In Progress (Partial)</t>
         </is>
       </c>
       <c r="H63" s="21" t="inlineStr">
@@ -4497,58 +4501,54 @@
         </is>
       </c>
       <c r="I63" s="33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J63" s="26" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="K63" s="21" t="inlineStr">
-        <is>
-          <t>Karthick</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J63" s="30" t="inlineStr">
+        <is>
+          <t>N/A (Upcoming)</t>
+        </is>
+      </c>
+      <c r="K63" s="21" t="n"/>
       <c r="L63" s="33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M63" s="24" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+        <v>1</v>
+      </c>
+      <c r="M63" s="30" t="inlineStr">
+        <is>
+          <t>N/A (Upcoming)</t>
         </is>
       </c>
       <c r="N63" s="21" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="21" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B64" s="21" t="inlineStr">
         <is>
-          <t>Grants</t>
+          <t>Field Collection</t>
         </is>
       </c>
       <c r="C64" s="21" t="inlineStr">
         <is>
-          <t>Grant Calendar</t>
+          <t>Field Collection</t>
         </is>
       </c>
       <c r="D64" s="21" t="inlineStr">
         <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="E64" s="29" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="E64" s="22" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F64" s="33" t="n">
         <v>0.75</v>
       </c>
-      <c r="G64" s="28" t="inlineStr">
-        <is>
-          <t>In Progress (Partial)</t>
+      <c r="G64" s="23" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
       <c r="H64" s="21" t="inlineStr">
@@ -4559,25 +4559,29 @@
       <c r="I64" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="J64" s="30" t="inlineStr">
-        <is>
-          <t>N/A (Upcoming)</t>
-        </is>
-      </c>
-      <c r="K64" s="21" t="n"/>
+      <c r="J64" s="26" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K64" s="21" t="inlineStr">
+        <is>
+          <t>Kavin</t>
+        </is>
+      </c>
       <c r="L64" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="M64" s="30" t="inlineStr">
-        <is>
-          <t>N/A (Upcoming)</t>
+      <c r="M64" s="24" t="inlineStr">
+        <is>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="N64" s="21" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="21" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B65" s="21" t="inlineStr">
         <is>
@@ -4586,12 +4590,12 @@
       </c>
       <c r="C65" s="21" t="inlineStr">
         <is>
-          <t>Field Collection</t>
+          <t>Receipt Book</t>
         </is>
       </c>
       <c r="D65" s="21" t="inlineStr">
         <is>
-          <t>FLOW</t>
+          <t>MASTER_GRID</t>
         </is>
       </c>
       <c r="E65" s="22" t="inlineStr">
@@ -4600,21 +4604,21 @@
         </is>
       </c>
       <c r="F65" s="33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G65" s="23" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H65" s="21" t="inlineStr">
+        <is>
+          <t>Karthick</t>
+        </is>
+      </c>
+      <c r="I65" s="33" t="n">
         <v>0.75</v>
       </c>
-      <c r="G65" s="23" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="H65" s="21" t="inlineStr">
-        <is>
-          <t>Karthick</t>
-        </is>
-      </c>
-      <c r="I65" s="33" t="n">
-        <v>1</v>
-      </c>
       <c r="J65" s="26" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -4626,7 +4630,7 @@
         </is>
       </c>
       <c r="L65" s="33" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="M65" s="24" t="inlineStr">
         <is>
@@ -4637,7 +4641,7 @@
     </row>
     <row r="66">
       <c r="A66" s="21" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B66" s="21" t="inlineStr">
         <is>
@@ -4646,21 +4650,21 @@
       </c>
       <c r="C66" s="21" t="inlineStr">
         <is>
-          <t>Receipt Book</t>
+          <t>Ambassador</t>
         </is>
       </c>
       <c r="D66" s="21" t="inlineStr">
         <is>
-          <t>MASTER_GRID</t>
-        </is>
-      </c>
-      <c r="E66" s="22" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="E66" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F66" s="33" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G66" s="23" t="inlineStr">
         <is>
@@ -4673,7 +4677,7 @@
         </is>
       </c>
       <c r="I66" s="33" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="J66" s="26" t="inlineStr">
         <is>
@@ -4686,7 +4690,7 @@
         </is>
       </c>
       <c r="L66" s="33" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="M66" s="24" t="inlineStr">
         <is>
@@ -4697,7 +4701,7 @@
     </row>
     <row r="67">
       <c r="A67" s="21" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B67" s="21" t="inlineStr">
         <is>
@@ -4706,21 +4710,21 @@
       </c>
       <c r="C67" s="21" t="inlineStr">
         <is>
-          <t>Ambassador</t>
+          <t>Ambassador Dashboard</t>
         </is>
       </c>
       <c r="D67" s="21" t="inlineStr">
         <is>
-          <t>FLOW</t>
-        </is>
-      </c>
-      <c r="E67" s="27" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="E67" s="29" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="F67" s="33" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="G67" s="23" t="inlineStr">
         <is>
@@ -4733,87 +4737,83 @@
         </is>
       </c>
       <c r="I67" s="33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J67" s="26" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="K67" s="21" t="inlineStr">
-        <is>
-          <t>Kavin</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J67" s="30" t="inlineStr">
+        <is>
+          <t>N/A (Upcoming)</t>
+        </is>
+      </c>
+      <c r="K67" s="21" t="n"/>
       <c r="L67" s="33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M67" s="24" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+        <v>1</v>
+      </c>
+      <c r="M67" s="30" t="inlineStr">
+        <is>
+          <t>N/A (Upcoming)</t>
         </is>
       </c>
       <c r="N67" s="21" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="21" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B68" s="21" t="inlineStr">
         <is>
-          <t>Field Collection</t>
+          <t>Administration</t>
         </is>
       </c>
       <c r="C68" s="21" t="inlineStr">
         <is>
-          <t>Ambassador Dashboard</t>
+          <t>Role Management (combined: Role + Capability + Role-Capability Matrix)</t>
         </is>
       </c>
       <c r="D68" s="21" t="inlineStr">
         <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="E68" s="29" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="E68" s="22" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F68" s="33" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G68" s="23" t="inlineStr">
-        <is>
-          <t>Completed</t>
+        <v>1</v>
+      </c>
+      <c r="G68" s="28" t="inlineStr">
+        <is>
+          <t>In Progress (Partial)</t>
         </is>
       </c>
       <c r="H68" s="21" t="inlineStr">
         <is>
-          <t>Karthick</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="I68" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J68" s="30" t="inlineStr">
-        <is>
-          <t>N/A (Upcoming)</t>
+        <v>1.5</v>
+      </c>
+      <c r="J68" s="24" t="inlineStr">
+        <is>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="K68" s="21" t="n"/>
       <c r="L68" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="M68" s="30" t="inlineStr">
-        <is>
-          <t>N/A (Upcoming)</t>
+        <v>1.5</v>
+      </c>
+      <c r="M68" s="24" t="inlineStr">
+        <is>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="N68" s="21" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="21" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B69" s="21" t="inlineStr">
         <is>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="C69" s="21" t="inlineStr">
         <is>
-          <t>Role Management (combined: Role + Capability + Role-Capability Matrix)</t>
+          <t>Menu Management</t>
         </is>
       </c>
       <c r="D69" s="21" t="inlineStr">
         <is>
-          <t>Config</t>
+          <t>MASTER_GRID</t>
         </is>
       </c>
       <c r="E69" s="22" t="inlineStr">
@@ -4836,7 +4836,7 @@
         </is>
       </c>
       <c r="F69" s="33" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="G69" s="28" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         </is>
       </c>
       <c r="I69" s="33" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J69" s="24" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="K69" s="21" t="n"/>
       <c r="L69" s="33" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M69" s="24" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
     </row>
     <row r="70">
       <c r="A70" s="21" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B70" s="21" t="inlineStr">
         <is>
@@ -4878,21 +4878,21 @@
       </c>
       <c r="C70" s="21" t="inlineStr">
         <is>
-          <t>Menu Management</t>
+          <t>User Management</t>
         </is>
       </c>
       <c r="D70" s="21" t="inlineStr">
         <is>
-          <t>MASTER_GRID</t>
-        </is>
-      </c>
-      <c r="E70" s="22" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="E70" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F70" s="33" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G70" s="28" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         </is>
       </c>
       <c r="I70" s="33" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J70" s="24" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="K70" s="21" t="n"/>
       <c r="L70" s="33" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M70" s="24" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
     </row>
     <row r="71">
       <c r="A71" s="21" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B71" s="21" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="C71" s="21" t="inlineStr">
         <is>
-          <t>User Management</t>
+          <t>Audit Trail</t>
         </is>
       </c>
       <c r="D71" s="21" t="inlineStr">
@@ -4942,9 +4942,9 @@
           <t>FLOW</t>
         </is>
       </c>
-      <c r="E71" s="27" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="E71" s="22" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F71" s="33" t="n">
@@ -4957,11 +4957,11 @@
       </c>
       <c r="H71" s="21" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Karthick</t>
         </is>
       </c>
       <c r="I71" s="33" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J71" s="24" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="K71" s="21" t="n"/>
       <c r="L71" s="33" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M71" s="24" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
     </row>
     <row r="72">
       <c r="A72" s="21" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B72" s="21" t="inlineStr">
         <is>
@@ -4990,12 +4990,12 @@
       </c>
       <c r="C72" s="21" t="inlineStr">
         <is>
-          <t>Audit Trail</t>
+          <t>Company Settings</t>
         </is>
       </c>
       <c r="D72" s="21" t="inlineStr">
         <is>
-          <t>FLOW</t>
+          <t>Config</t>
         </is>
       </c>
       <c r="E72" s="22" t="inlineStr">
@@ -5004,20 +5004,20 @@
         </is>
       </c>
       <c r="F72" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="G72" s="28" t="inlineStr">
-        <is>
-          <t>In Progress (Partial)</t>
+        <v>1.5</v>
+      </c>
+      <c r="G72" s="23" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
       <c r="H72" s="21" t="inlineStr">
         <is>
-          <t>Karthick</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="I72" s="33" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J72" s="24" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="K72" s="21" t="n"/>
       <c r="L72" s="33" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M72" s="24" t="inlineStr">
         <is>
@@ -5036,22 +5036,24 @@
       <c r="N72" s="21" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="21" t="n">
-        <v>75</v>
+      <c r="A73" s="21" t="inlineStr">
+        <is>
+          <t>76, 162</t>
+        </is>
       </c>
       <c r="B73" s="21" t="inlineStr">
         <is>
-          <t>Administration</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="C73" s="21" t="inlineStr">
         <is>
-          <t>Company Settings</t>
+          <t>Master Data (combined: Master Data + Master Data Type)</t>
         </is>
       </c>
       <c r="D73" s="21" t="inlineStr">
         <is>
-          <t>Config</t>
+          <t>MASTER_GRID</t>
         </is>
       </c>
       <c r="E73" s="22" t="inlineStr">
@@ -5060,7 +5062,7 @@
         </is>
       </c>
       <c r="F73" s="33" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="G73" s="23" t="inlineStr">
         <is>
@@ -5069,11 +5071,11 @@
       </c>
       <c r="H73" s="21" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Karthick</t>
         </is>
       </c>
       <c r="I73" s="33" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J73" s="24" t="inlineStr">
         <is>
@@ -5082,7 +5084,7 @@
       </c>
       <c r="K73" s="21" t="n"/>
       <c r="L73" s="33" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M73" s="24" t="inlineStr">
         <is>
@@ -5092,10 +5094,8 @@
       <c r="N73" s="21" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="21" t="inlineStr">
-        <is>
-          <t>76, 162</t>
-        </is>
+      <c r="A74" s="21" t="n">
+        <v>77</v>
       </c>
       <c r="B74" s="21" t="inlineStr">
         <is>
@@ -5104,12 +5104,12 @@
       </c>
       <c r="C74" s="21" t="inlineStr">
         <is>
-          <t>Master Data (combined: Master Data + Master Data Type)</t>
+          <t>Grid Config (combined: Grid Config + Field master + Custom Fields)</t>
         </is>
       </c>
       <c r="D74" s="21" t="inlineStr">
         <is>
-          <t>MASTER_GRID</t>
+          <t>Config</t>
         </is>
       </c>
       <c r="E74" s="22" t="inlineStr">
@@ -5120,14 +5120,14 @@
       <c r="F74" s="33" t="n">
         <v>0.75</v>
       </c>
-      <c r="G74" s="23" t="inlineStr">
-        <is>
-          <t>Completed</t>
+      <c r="G74" s="28" t="inlineStr">
+        <is>
+          <t>In Progress (Partial)</t>
         </is>
       </c>
       <c r="H74" s="21" t="inlineStr">
         <is>
-          <t>Karthick</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="I74" s="33" t="n">
@@ -5151,7 +5151,7 @@
     </row>
     <row r="75">
       <c r="A75" s="21" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B75" s="21" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="C75" s="21" t="inlineStr">
         <is>
-          <t>Grid Config (combined: Grid Config + Field master + Custom Fields)</t>
+          <t>Dashboard Config (combined: Dashboard Config + Dashboard Layout + Widget cluster)</t>
         </is>
       </c>
       <c r="D75" s="21" t="inlineStr">
@@ -5207,7 +5207,7 @@
     </row>
     <row r="76">
       <c r="A76" s="21" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B76" s="21" t="inlineStr">
         <is>
@@ -5216,12 +5216,12 @@
       </c>
       <c r="C76" s="21" t="inlineStr">
         <is>
-          <t>Dashboard Config (combined: Dashboard Config + Dashboard Layout + Widget cluster)</t>
+          <t>Currency Management</t>
         </is>
       </c>
       <c r="D76" s="21" t="inlineStr">
         <is>
-          <t>Config</t>
+          <t>MASTER_GRID</t>
         </is>
       </c>
       <c r="E76" s="22" t="inlineStr">
@@ -5230,20 +5230,20 @@
         </is>
       </c>
       <c r="F76" s="33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G76" s="24" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H76" s="21" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I76" s="33" t="n">
         <v>0.75</v>
-      </c>
-      <c r="G76" s="28" t="inlineStr">
-        <is>
-          <t>In Progress (Partial)</t>
-        </is>
-      </c>
-      <c r="H76" s="21" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="I76" s="33" t="n">
-        <v>1</v>
       </c>
       <c r="J76" s="24" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="K76" s="21" t="n"/>
       <c r="L76" s="33" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="M76" s="24" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
     </row>
     <row r="77">
       <c r="A77" s="21" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B77" s="21" t="inlineStr">
         <is>
@@ -5272,12 +5272,12 @@
       </c>
       <c r="C77" s="21" t="inlineStr">
         <is>
-          <t>Currency Management</t>
+          <t>Region Hierarchy</t>
         </is>
       </c>
       <c r="D77" s="21" t="inlineStr">
         <is>
-          <t>MASTER_GRID</t>
+          <t>Config</t>
         </is>
       </c>
       <c r="E77" s="22" t="inlineStr">
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="F77" s="33" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G77" s="24" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         </is>
       </c>
       <c r="I77" s="33" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="J77" s="24" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="K77" s="21" t="n"/>
       <c r="L77" s="33" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="M77" s="24" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
     </row>
     <row r="78">
       <c r="A78" s="21" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B78" s="21" t="inlineStr">
         <is>
@@ -5328,21 +5328,21 @@
       </c>
       <c r="C78" s="21" t="inlineStr">
         <is>
-          <t>Region Hierarchy</t>
+          <t>Document Types</t>
         </is>
       </c>
       <c r="D78" s="21" t="inlineStr">
         <is>
-          <t>Config</t>
-        </is>
-      </c>
-      <c r="E78" s="22" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>MASTER_GRID</t>
+        </is>
+      </c>
+      <c r="E78" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F78" s="33" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G78" s="24" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         </is>
       </c>
       <c r="I78" s="33" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="J78" s="24" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="K78" s="21" t="n"/>
       <c r="L78" s="33" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="M78" s="24" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
     </row>
     <row r="79">
       <c r="A79" s="21" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B79" s="21" t="inlineStr">
         <is>
@@ -5384,25 +5384,25 @@
       </c>
       <c r="C79" s="21" t="inlineStr">
         <is>
-          <t>Document Types</t>
+          <t>Certificate Templates</t>
         </is>
       </c>
       <c r="D79" s="21" t="inlineStr">
         <is>
-          <t>MASTER_GRID</t>
-        </is>
-      </c>
-      <c r="E79" s="27" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="E79" s="22" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F79" s="33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G79" s="24" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+        <v>0.75</v>
+      </c>
+      <c r="G79" s="28" t="inlineStr">
+        <is>
+          <t>In Progress (Partial)</t>
         </is>
       </c>
       <c r="H79" s="21" t="inlineStr">
@@ -5411,7 +5411,7 @@
         </is>
       </c>
       <c r="I79" s="33" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="J79" s="24" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="K79" s="21" t="n"/>
       <c r="L79" s="33" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="M79" s="24" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
     </row>
     <row r="80">
       <c r="A80" s="21" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B80" s="21" t="inlineStr">
         <is>
@@ -5440,12 +5440,12 @@
       </c>
       <c r="C80" s="21" t="inlineStr">
         <is>
-          <t>Certificate Templates</t>
+          <t>Email Provider Config</t>
         </is>
       </c>
       <c r="D80" s="21" t="inlineStr">
         <is>
-          <t>FLOW</t>
+          <t>Config</t>
         </is>
       </c>
       <c r="E80" s="22" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="H80" s="21" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Karthick</t>
         </is>
       </c>
       <c r="I80" s="33" t="n">
@@ -5486,8 +5486,10 @@
       <c r="N80" s="21" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="21" t="n">
-        <v>84</v>
+      <c r="A81" s="21" t="inlineStr">
+        <is>
+          <t>85, 165-166</t>
+        </is>
       </c>
       <c r="B81" s="21" t="inlineStr">
         <is>
@@ -5496,7 +5498,7 @@
       </c>
       <c r="C81" s="21" t="inlineStr">
         <is>
-          <t>Email Provider Config</t>
+          <t>Organization Settings (combined: Org Settings + Setting Group + User Setting)</t>
         </is>
       </c>
       <c r="D81" s="21" t="inlineStr">
@@ -5512,14 +5514,14 @@
       <c r="F81" s="33" t="n">
         <v>0.75</v>
       </c>
-      <c r="G81" s="28" t="inlineStr">
-        <is>
-          <t>In Progress (Partial)</t>
+      <c r="G81" s="24" t="inlineStr">
+        <is>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="H81" s="21" t="inlineStr">
         <is>
-          <t>Karthick</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="I81" s="33" t="n">
@@ -5542,10 +5544,8 @@
       <c r="N81" s="21" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="21" t="inlineStr">
-        <is>
-          <t>85, 165-166</t>
-        </is>
+      <c r="A82" s="21" t="n">
+        <v>86</v>
       </c>
       <c r="B82" s="21" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
       </c>
       <c r="C82" s="21" t="inlineStr">
         <is>
-          <t>Organization Settings (combined: Org Settings + Setting Group + User Setting)</t>
+          <t>API Management</t>
         </is>
       </c>
       <c r="D82" s="21" t="inlineStr">
@@ -5562,13 +5562,13 @@
           <t>Config</t>
         </is>
       </c>
-      <c r="E82" s="22" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="E82" s="29" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="F82" s="33" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G82" s="24" t="inlineStr">
         <is>
@@ -5577,31 +5577,31 @@
       </c>
       <c r="H82" s="21" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>N/A (Upcoming)</t>
         </is>
       </c>
       <c r="I82" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J82" s="24" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+        <v>1.5</v>
+      </c>
+      <c r="J82" s="30" t="inlineStr">
+        <is>
+          <t>N/A (Upcoming)</t>
         </is>
       </c>
       <c r="K82" s="21" t="n"/>
       <c r="L82" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="M82" s="24" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+        <v>1.5</v>
+      </c>
+      <c r="M82" s="30" t="inlineStr">
+        <is>
+          <t>N/A (Upcoming)</t>
         </is>
       </c>
       <c r="N82" s="21" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="21" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B83" s="21" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="C83" s="21" t="inlineStr">
         <is>
-          <t>API Management</t>
+          <t>Integration Marketplace</t>
         </is>
       </c>
       <c r="D83" s="21" t="inlineStr">
@@ -5657,7 +5657,7 @@
     </row>
     <row r="84">
       <c r="A84" s="21" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B84" s="21" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="C84" s="21" t="inlineStr">
         <is>
-          <t>Integration Marketplace</t>
+          <t>Accounting Integration</t>
         </is>
       </c>
       <c r="D84" s="21" t="inlineStr">
@@ -5713,7 +5713,7 @@
     </row>
     <row r="85">
       <c r="A85" s="21" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B85" s="21" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="C85" s="21" t="inlineStr">
         <is>
-          <t>Accounting Integration</t>
+          <t>Social Media Integration</t>
         </is>
       </c>
       <c r="D85" s="21" t="inlineStr">
@@ -5769,21 +5769,21 @@
     </row>
     <row r="86">
       <c r="A86" s="21" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B86" s="21" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>AI Intelligence</t>
         </is>
       </c>
       <c r="C86" s="21" t="inlineStr">
         <is>
-          <t>Social Media Integration</t>
+          <t>Engagement Scoring</t>
         </is>
       </c>
       <c r="D86" s="21" t="inlineStr">
         <is>
-          <t>Config</t>
+          <t>FLOW</t>
         </is>
       </c>
       <c r="E86" s="29" t="inlineStr">
@@ -5792,7 +5792,7 @@
         </is>
       </c>
       <c r="F86" s="33" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="G86" s="24" t="inlineStr">
         <is>
@@ -5801,31 +5801,31 @@
       </c>
       <c r="H86" s="21" t="inlineStr">
         <is>
-          <t>N/A (Upcoming)</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="I86" s="33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J86" s="30" t="inlineStr">
-        <is>
-          <t>N/A (Upcoming)</t>
+        <v>3</v>
+      </c>
+      <c r="J86" s="24" t="inlineStr">
+        <is>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="K86" s="21" t="n"/>
       <c r="L86" s="33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M86" s="30" t="inlineStr">
-        <is>
-          <t>N/A (Upcoming)</t>
+        <v>3</v>
+      </c>
+      <c r="M86" s="24" t="inlineStr">
+        <is>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="N86" s="21" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="21" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B87" s="21" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="C87" s="21" t="inlineStr">
         <is>
-          <t>Engagement Scoring</t>
+          <t>Churn Prediction</t>
         </is>
       </c>
       <c r="D87" s="21" t="inlineStr">
@@ -5881,7 +5881,7 @@
     </row>
     <row r="88">
       <c r="A88" s="21" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B88" s="21" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C88" s="21" t="inlineStr">
         <is>
-          <t>Churn Prediction</t>
+          <t>Action Board</t>
         </is>
       </c>
       <c r="D88" s="21" t="inlineStr">
@@ -5937,7 +5937,7 @@
     </row>
     <row r="89">
       <c r="A89" s="21" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B89" s="21" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="C89" s="21" t="inlineStr">
         <is>
-          <t>Action Board</t>
+          <t>AI Draft</t>
         </is>
       </c>
       <c r="D89" s="21" t="inlineStr">
@@ -5969,31 +5969,31 @@
       </c>
       <c r="H89" s="21" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>N/A (Upcoming)</t>
         </is>
       </c>
       <c r="I89" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="J89" s="24" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J89" s="30" t="inlineStr">
+        <is>
+          <t>N/A (Upcoming)</t>
         </is>
       </c>
       <c r="K89" s="21" t="n"/>
       <c r="L89" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="M89" s="24" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="M89" s="30" t="inlineStr">
+        <is>
+          <t>N/A (Upcoming)</t>
         </is>
       </c>
       <c r="N89" s="21" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="21" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B90" s="21" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
       </c>
       <c r="C90" s="21" t="inlineStr">
         <is>
-          <t>AI Draft</t>
+          <t>NL Reporting</t>
         </is>
       </c>
       <c r="D90" s="21" t="inlineStr">
@@ -6049,7 +6049,7 @@
     </row>
     <row r="91">
       <c r="A91" s="21" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B91" s="21" t="inlineStr">
         <is>
@@ -6058,12 +6058,12 @@
       </c>
       <c r="C91" s="21" t="inlineStr">
         <is>
-          <t>NL Reporting</t>
+          <t>Predictive Analytics</t>
         </is>
       </c>
       <c r="D91" s="21" t="inlineStr">
         <is>
-          <t>FLOW</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="E91" s="29" t="inlineStr">
@@ -6105,63 +6105,63 @@
     </row>
     <row r="92">
       <c r="A92" s="21" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B92" s="21" t="inlineStr">
         <is>
-          <t>AI Intelligence</t>
+          <t>Reports</t>
         </is>
       </c>
       <c r="C92" s="21" t="inlineStr">
         <is>
-          <t>Predictive Analytics</t>
+          <t>Custom Report Builder</t>
         </is>
       </c>
       <c r="D92" s="21" t="inlineStr">
         <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="E92" s="29" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="E92" s="22" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F92" s="33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G92" s="24" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+        <v>1</v>
+      </c>
+      <c r="G92" s="23" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
       <c r="H92" s="21" t="inlineStr">
         <is>
-          <t>N/A (Upcoming)</t>
+          <t>Karthick</t>
         </is>
       </c>
       <c r="I92" s="33" t="n">
-        <v>3</v>
-      </c>
-      <c r="J92" s="30" t="inlineStr">
-        <is>
-          <t>N/A (Upcoming)</t>
+        <v>1.5</v>
+      </c>
+      <c r="J92" s="24" t="inlineStr">
+        <is>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="K92" s="21" t="n"/>
       <c r="L92" s="33" t="n">
-        <v>3</v>
-      </c>
-      <c r="M92" s="30" t="inlineStr">
-        <is>
-          <t>N/A (Upcoming)</t>
+        <v>1.5</v>
+      </c>
+      <c r="M92" s="24" t="inlineStr">
+        <is>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="N92" s="21" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="21" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B93" s="21" t="inlineStr">
         <is>
@@ -6170,12 +6170,12 @@
       </c>
       <c r="C93" s="21" t="inlineStr">
         <is>
-          <t>Custom Report Builder</t>
+          <t>PowerBI Viewer</t>
         </is>
       </c>
       <c r="D93" s="21" t="inlineStr">
         <is>
-          <t>FLOW</t>
+          <t>Config</t>
         </is>
       </c>
       <c r="E93" s="22" t="inlineStr">
@@ -6184,20 +6184,20 @@
         </is>
       </c>
       <c r="F93" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="G93" s="23" t="inlineStr">
-        <is>
-          <t>Completed</t>
+        <v>0.75</v>
+      </c>
+      <c r="G93" s="28" t="inlineStr">
+        <is>
+          <t>In Progress (Partial)</t>
         </is>
       </c>
       <c r="H93" s="21" t="inlineStr">
         <is>
-          <t>Karthick</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="I93" s="33" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J93" s="24" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="K93" s="21" t="n"/>
       <c r="L93" s="33" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M93" s="24" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
     </row>
     <row r="94">
       <c r="A94" s="21" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B94" s="21" t="inlineStr">
         <is>
@@ -6226,54 +6226,54 @@
       </c>
       <c r="C94" s="21" t="inlineStr">
         <is>
-          <t>PowerBI Viewer</t>
+          <t>Donor Retention Dashboard</t>
         </is>
       </c>
       <c r="D94" s="21" t="inlineStr">
         <is>
-          <t>Config</t>
-        </is>
-      </c>
-      <c r="E94" s="22" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="E94" s="29" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="F94" s="33" t="n">
         <v>0.75</v>
       </c>
-      <c r="G94" s="28" t="inlineStr">
-        <is>
-          <t>In Progress (Partial)</t>
+      <c r="G94" s="23" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
       <c r="H94" s="21" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Karthick</t>
         </is>
       </c>
       <c r="I94" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="J94" s="24" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="J94" s="30" t="inlineStr">
+        <is>
+          <t>N/A (Upcoming)</t>
         </is>
       </c>
       <c r="K94" s="21" t="n"/>
       <c r="L94" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="M94" s="24" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+      <c r="M94" s="30" t="inlineStr">
+        <is>
+          <t>N/A (Upcoming)</t>
         </is>
       </c>
       <c r="N94" s="21" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="21" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B95" s="21" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="C95" s="21" t="inlineStr">
         <is>
-          <t>Donor Retention Dashboard</t>
+          <t>Report Catalog</t>
         </is>
       </c>
       <c r="D95" s="21" t="inlineStr">
@@ -6329,7 +6329,7 @@
     </row>
     <row r="96">
       <c r="A96" s="21" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B96" s="21" t="inlineStr">
         <is>
@@ -6338,12 +6338,12 @@
       </c>
       <c r="C96" s="21" t="inlineStr">
         <is>
-          <t>Report Catalog</t>
+          <t>HTML Report Viewer</t>
         </is>
       </c>
       <c r="D96" s="21" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Config</t>
         </is>
       </c>
       <c r="E96" s="29" t="inlineStr">
@@ -6352,20 +6352,20 @@
         </is>
       </c>
       <c r="F96" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" s="23" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H96" s="21" t="inlineStr">
+        <is>
+          <t>Karthick</t>
+        </is>
+      </c>
+      <c r="I96" s="33" t="n">
         <v>0.75</v>
-      </c>
-      <c r="G96" s="23" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="H96" s="21" t="inlineStr">
-        <is>
-          <t>Karthick</t>
-        </is>
-      </c>
-      <c r="I96" s="33" t="n">
-        <v>1</v>
       </c>
       <c r="J96" s="30" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
       </c>
       <c r="K96" s="21" t="n"/>
       <c r="L96" s="33" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="M96" s="30" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
     </row>
     <row r="97">
       <c r="A97" s="21" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B97" s="21" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="C97" s="21" t="inlineStr">
         <is>
-          <t>HTML Report Viewer</t>
+          <t>Scheduled Reports</t>
         </is>
       </c>
       <c r="D97" s="21" t="inlineStr">
@@ -6408,20 +6408,20 @@
         </is>
       </c>
       <c r="F97" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="G97" s="23" t="inlineStr">
-        <is>
-          <t>Completed</t>
+        <v>0.75</v>
+      </c>
+      <c r="G97" s="24" t="inlineStr">
+        <is>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="H97" s="21" t="inlineStr">
         <is>
-          <t>Karthick</t>
+          <t>N/A (Upcoming)</t>
         </is>
       </c>
       <c r="I97" s="33" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="J97" s="30" t="inlineStr">
         <is>
@@ -6430,138 +6430,138 @@
       </c>
       <c r="K97" s="21" t="n"/>
       <c r="L97" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M97" s="30" t="inlineStr">
+        <is>
+          <t>N/A (Upcoming)</t>
+        </is>
+      </c>
+      <c r="N97" s="21" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="21" t="inlineStr">
+        <is>
+          <t>102-118</t>
+        </is>
+      </c>
+      <c r="B98" s="21" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="C98" s="21" t="inlineStr">
+        <is>
+          <t>Donor App (8 screens) + Agent App (9 screens)</t>
+        </is>
+      </c>
+      <c r="D98" s="21" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="E98" s="29" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F98" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G98" s="24" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H98" s="21" t="inlineStr">
+        <is>
+          <t>N/A (Upcoming)</t>
+        </is>
+      </c>
+      <c r="I98" s="33" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J98" s="30" t="inlineStr">
+        <is>
+          <t>N/A (Upcoming)</t>
+        </is>
+      </c>
+      <c r="K98" s="21" t="n"/>
+      <c r="L98" s="33" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M98" s="30" t="inlineStr">
+        <is>
+          <t>N/A (Upcoming)</t>
+        </is>
+      </c>
+      <c r="N98" s="21" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="21" t="n">
+        <v>119</v>
+      </c>
+      <c r="B99" s="21" t="inlineStr">
+        <is>
+          <t>Root / Layout</t>
+        </is>
+      </c>
+      <c r="C99" s="21" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="D99" s="21" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="E99" s="22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F99" s="33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G99" s="24" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H99" s="21" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I99" s="33" t="n">
         <v>0.75</v>
       </c>
-      <c r="M97" s="30" t="inlineStr">
-        <is>
-          <t>N/A (Upcoming)</t>
-        </is>
-      </c>
-      <c r="N97" s="21" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="21" t="n">
-        <v>101</v>
-      </c>
-      <c r="B98" s="21" t="inlineStr">
-        <is>
-          <t>Reports</t>
-        </is>
-      </c>
-      <c r="C98" s="21" t="inlineStr">
-        <is>
-          <t>Scheduled Reports</t>
-        </is>
-      </c>
-      <c r="D98" s="21" t="inlineStr">
-        <is>
-          <t>Config</t>
-        </is>
-      </c>
-      <c r="E98" s="29" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F98" s="33" t="n">
+      <c r="J99" s="24" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K99" s="21" t="n"/>
+      <c r="L99" s="33" t="n">
         <v>0.75</v>
       </c>
-      <c r="G98" s="24" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H98" s="21" t="inlineStr">
-        <is>
-          <t>N/A (Upcoming)</t>
-        </is>
-      </c>
-      <c r="I98" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J98" s="30" t="inlineStr">
-        <is>
-          <t>N/A (Upcoming)</t>
-        </is>
-      </c>
-      <c r="K98" s="21" t="n"/>
-      <c r="L98" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="M98" s="30" t="inlineStr">
-        <is>
-          <t>N/A (Upcoming)</t>
-        </is>
-      </c>
-      <c r="N98" s="21" t="n"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="21" t="inlineStr">
-        <is>
-          <t>102-118</t>
-        </is>
-      </c>
-      <c r="B99" s="21" t="inlineStr">
-        <is>
-          <t>Mobile</t>
-        </is>
-      </c>
-      <c r="C99" s="21" t="inlineStr">
-        <is>
-          <t>Donor App (8 screens) + Agent App (9 screens)</t>
-        </is>
-      </c>
-      <c r="D99" s="21" t="inlineStr">
-        <is>
-          <t>Mobile</t>
-        </is>
-      </c>
-      <c r="E99" s="29" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F99" s="33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G99" s="24" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H99" s="21" t="inlineStr">
-        <is>
-          <t>N/A (Upcoming)</t>
-        </is>
-      </c>
-      <c r="I99" s="33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J99" s="30" t="inlineStr">
-        <is>
-          <t>N/A (Upcoming)</t>
-        </is>
-      </c>
-      <c r="K99" s="21" t="n"/>
-      <c r="L99" s="33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M99" s="30" t="inlineStr">
-        <is>
-          <t>N/A (Upcoming)</t>
+      <c r="M99" s="24" t="inlineStr">
+        <is>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="N99" s="21" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="21" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B100" s="21" t="inlineStr">
         <is>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="C100" s="21" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Main Dashboard</t>
         </is>
       </c>
       <c r="D100" s="21" t="inlineStr">
         <is>
-          <t>Auth</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="E100" s="22" t="inlineStr">
@@ -6584,7 +6584,7 @@
         </is>
       </c>
       <c r="F100" s="33" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G100" s="24" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         </is>
       </c>
       <c r="I100" s="33" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="J100" s="24" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="K100" s="21" t="n"/>
       <c r="L100" s="33" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="M100" s="24" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
     </row>
     <row r="101">
       <c r="A101" s="21" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B101" s="21" t="inlineStr">
         <is>
@@ -6626,12 +6626,12 @@
       </c>
       <c r="C101" s="21" t="inlineStr">
         <is>
-          <t>Main Dashboard</t>
+          <t>App Layout</t>
         </is>
       </c>
       <c r="D101" s="21" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Layout</t>
         </is>
       </c>
       <c r="E101" s="22" t="inlineStr">
@@ -6640,7 +6640,7 @@
         </is>
       </c>
       <c r="F101" s="33" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="G101" s="24" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         </is>
       </c>
       <c r="I101" s="33" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J101" s="24" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="K101" s="21" t="n"/>
       <c r="L101" s="33" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M101" s="24" t="inlineStr">
         <is>
@@ -6673,21 +6673,21 @@
     </row>
     <row r="102">
       <c r="A102" s="21" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B102" s="21" t="inlineStr">
         <is>
-          <t>Root / Layout</t>
+          <t>Contacts</t>
         </is>
       </c>
       <c r="C102" s="21" t="inlineStr">
         <is>
-          <t>App Layout</t>
+          <t>Contact Source</t>
         </is>
       </c>
       <c r="D102" s="21" t="inlineStr">
         <is>
-          <t>Layout</t>
+          <t>MASTER_GRID</t>
         </is>
       </c>
       <c r="E102" s="22" t="inlineStr">
@@ -6696,29 +6696,33 @@
         </is>
       </c>
       <c r="F102" s="33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G102" s="23" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H102" s="21" t="inlineStr">
+        <is>
+          <t>Karthick</t>
+        </is>
+      </c>
+      <c r="I102" s="33" t="n">
         <v>0.75</v>
       </c>
-      <c r="G102" s="24" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H102" s="21" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="I102" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J102" s="24" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K102" s="21" t="n"/>
+      <c r="J102" s="23" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="K102" s="21" t="inlineStr">
+        <is>
+          <t>Karthick</t>
+        </is>
+      </c>
       <c r="L102" s="33" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="M102" s="24" t="inlineStr">
         <is>
@@ -6728,22 +6732,22 @@
       <c r="N102" s="21" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="21" t="n">
-        <v>122</v>
-      </c>
-      <c r="B103" s="21" t="inlineStr">
+      <c r="A103" s="32" t="n">
+        <v>123</v>
+      </c>
+      <c r="B103" s="25" t="inlineStr">
         <is>
           <t>Contacts</t>
         </is>
       </c>
-      <c r="C103" s="21" t="inlineStr">
-        <is>
-          <t>Contact Source</t>
-        </is>
-      </c>
-      <c r="D103" s="21" t="inlineStr">
-        <is>
-          <t>MASTER_GRID</t>
+      <c r="C103" s="25" t="inlineStr">
+        <is>
+          <t>Contact Dashboard</t>
+        </is>
+      </c>
+      <c r="D103" s="25" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="E103" s="22" t="inlineStr">
@@ -6752,7 +6756,7 @@
         </is>
       </c>
       <c r="F103" s="33" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G103" s="23" t="inlineStr">
         <is>
@@ -6765,40 +6769,36 @@
         </is>
       </c>
       <c r="I103" s="33" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="J103" s="23" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="K103" s="21" t="inlineStr">
-        <is>
-          <t>Karthick</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J103" s="24" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K103" s="25" t="n"/>
       <c r="L103" s="33" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="M103" s="24" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="N103" s="21" t="n"/>
+      <c r="N103" s="25" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="32" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B104" s="25" t="inlineStr">
         <is>
-          <t>Contacts</t>
+          <t>Fundraising</t>
         </is>
       </c>
       <c r="C104" s="25" t="inlineStr">
         <is>
-          <t>Contact Dashboard</t>
+          <t>Donation Dashboard</t>
         </is>
       </c>
       <c r="D104" s="25" t="inlineStr">
@@ -6845,16 +6845,16 @@
     </row>
     <row r="105">
       <c r="A105" s="32" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B105" s="25" t="inlineStr">
         <is>
-          <t>Fundraising</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="C105" s="25" t="inlineStr">
         <is>
-          <t>Donation Dashboard</t>
+          <t>Communication Dashboard</t>
         </is>
       </c>
       <c r="D105" s="25" t="inlineStr">
@@ -6875,7 +6875,7 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="H105" s="21" t="inlineStr">
+      <c r="H105" s="25" t="inlineStr">
         <is>
           <t>Karthick</t>
         </is>
@@ -6901,43 +6901,43 @@
     </row>
     <row r="106">
       <c r="A106" s="32" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B106" s="25" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Administration</t>
         </is>
       </c>
       <c r="C106" s="25" t="inlineStr">
         <is>
-          <t>Communication Dashboard</t>
+          <t>Modules</t>
         </is>
       </c>
       <c r="D106" s="25" t="inlineStr">
         <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="E106" s="22" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>MASTER_GRID</t>
+        </is>
+      </c>
+      <c r="E106" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F106" s="33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G106" s="23" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H106" s="25" t="inlineStr">
+        <is>
+          <t>Karthick</t>
+        </is>
+      </c>
+      <c r="I106" s="33" t="n">
         <v>0.75</v>
-      </c>
-      <c r="G106" s="23" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="H106" s="25" t="inlineStr">
-        <is>
-          <t>Karthick</t>
-        </is>
-      </c>
-      <c r="I106" s="33" t="n">
-        <v>1</v>
       </c>
       <c r="J106" s="24" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="K106" s="25" t="n"/>
       <c r="L106" s="33" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="M106" s="24" t="inlineStr">
         <is>
@@ -6957,43 +6957,43 @@
     </row>
     <row r="107">
       <c r="A107" s="32" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B107" s="25" t="inlineStr">
         <is>
-          <t>Administration</t>
+          <t>Certificate</t>
         </is>
       </c>
       <c r="C107" s="25" t="inlineStr">
         <is>
-          <t>Modules</t>
+          <t>Certificate Management (combined: Process + Print)</t>
         </is>
       </c>
       <c r="D107" s="25" t="inlineStr">
         <is>
-          <t>MASTER_GRID</t>
-        </is>
-      </c>
-      <c r="E107" s="27" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="E107" s="22" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F107" s="33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G107" s="23" t="inlineStr">
-        <is>
-          <t>Completed</t>
+        <v>0.75</v>
+      </c>
+      <c r="G107" s="24" t="inlineStr">
+        <is>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="H107" s="25" t="inlineStr">
         <is>
-          <t>Karthick</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="I107" s="33" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="J107" s="24" t="inlineStr">
         <is>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="K107" s="25" t="n"/>
       <c r="L107" s="33" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="M107" s="24" t="inlineStr">
         <is>
@@ -7013,21 +7013,21 @@
     </row>
     <row r="108">
       <c r="A108" s="32" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B108" s="25" t="inlineStr">
         <is>
-          <t>Certificate</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="C108" s="25" t="inlineStr">
         <is>
-          <t>Certificate Management (combined: Process + Print)</t>
+          <t>Email Keywords</t>
         </is>
       </c>
       <c r="D108" s="25" t="inlineStr">
         <is>
-          <t>FLOW</t>
+          <t>MASTER_GRID</t>
         </is>
       </c>
       <c r="E108" s="22" t="inlineStr">
@@ -7036,20 +7036,20 @@
         </is>
       </c>
       <c r="F108" s="33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G108" s="24" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H108" s="25" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I108" s="33" t="n">
         <v>0.75</v>
-      </c>
-      <c r="G108" s="24" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H108" s="25" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="I108" s="33" t="n">
-        <v>1</v>
       </c>
       <c r="J108" s="24" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="K108" s="25" t="n"/>
       <c r="L108" s="33" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="M108" s="24" t="inlineStr">
         <is>
@@ -7069,21 +7069,21 @@
     </row>
     <row r="109">
       <c r="A109" s="32" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B109" s="25" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Field Collection</t>
         </is>
       </c>
       <c r="C109" s="25" t="inlineStr">
         <is>
-          <t>Email Keywords</t>
+          <t>Record Collection</t>
         </is>
       </c>
       <c r="D109" s="25" t="inlineStr">
         <is>
-          <t>MASTER_GRID</t>
+          <t>FLOW</t>
         </is>
       </c>
       <c r="E109" s="22" t="inlineStr">
@@ -7092,7 +7092,7 @@
         </is>
       </c>
       <c r="F109" s="33" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G109" s="24" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="I109" s="33" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="J109" s="24" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
       </c>
       <c r="K109" s="25" t="n"/>
       <c r="L109" s="33" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="M109" s="24" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
     </row>
     <row r="110">
       <c r="A110" s="32" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B110" s="25" t="inlineStr">
         <is>
@@ -7134,12 +7134,12 @@
       </c>
       <c r="C110" s="25" t="inlineStr">
         <is>
-          <t>Record Collection</t>
+          <t>Ambassador Performance</t>
         </is>
       </c>
       <c r="D110" s="25" t="inlineStr">
         <is>
-          <t>FLOW</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="E110" s="22" t="inlineStr">
@@ -7181,21 +7181,21 @@
     </row>
     <row r="111">
       <c r="A111" s="32" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B111" s="25" t="inlineStr">
         <is>
-          <t>Field Collection</t>
+          <t>Fundraising</t>
         </is>
       </c>
       <c r="C111" s="25" t="inlineStr">
         <is>
-          <t>Ambassador Performance</t>
+          <t>P2P Fundraisers</t>
         </is>
       </c>
       <c r="D111" s="25" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>FLOW</t>
         </is>
       </c>
       <c r="E111" s="22" t="inlineStr">
@@ -7204,20 +7204,20 @@
         </is>
       </c>
       <c r="F111" s="33" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G111" s="24" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+        <v>1</v>
+      </c>
+      <c r="G111" s="23" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
       <c r="H111" s="25" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Karthick</t>
         </is>
       </c>
       <c r="I111" s="33" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J111" s="24" t="inlineStr">
         <is>
@@ -7226,7 +7226,7 @@
       </c>
       <c r="K111" s="25" t="n"/>
       <c r="L111" s="33" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M111" s="24" t="inlineStr">
         <is>
@@ -7237,16 +7237,16 @@
     </row>
     <row r="112">
       <c r="A112" s="32" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B112" s="25" t="inlineStr">
         <is>
-          <t>Fundraising</t>
+          <t>Prayer Request</t>
         </is>
       </c>
       <c r="C112" s="25" t="inlineStr">
         <is>
-          <t>P2P Fundraisers</t>
+          <t>Prayer Request Entry</t>
         </is>
       </c>
       <c r="D112" s="25" t="inlineStr">
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="F112" s="33" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="G112" s="23" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         </is>
       </c>
       <c r="I112" s="33" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J112" s="24" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
       </c>
       <c r="K112" s="25" t="n"/>
       <c r="L112" s="33" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M112" s="24" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
     </row>
     <row r="113">
       <c r="A113" s="32" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B113" s="25" t="inlineStr">
         <is>
@@ -7302,7 +7302,7 @@
       </c>
       <c r="C113" s="25" t="inlineStr">
         <is>
-          <t>Prayer Request Entry</t>
+          <t>Reply Queue</t>
         </is>
       </c>
       <c r="D113" s="25" t="inlineStr">
@@ -7349,7 +7349,7 @@
     </row>
     <row r="114">
       <c r="A114" s="32" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B114" s="25" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="C114" s="25" t="inlineStr">
         <is>
-          <t>Reply Queue</t>
+          <t>Review Reply</t>
         </is>
       </c>
       <c r="D114" s="25" t="inlineStr">
@@ -7405,43 +7405,43 @@
     </row>
     <row r="115">
       <c r="A115" s="32" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B115" s="25" t="inlineStr">
         <is>
-          <t>Prayer Request</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C115" s="25" t="inlineStr">
         <is>
-          <t>Review Reply</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="D115" s="25" t="inlineStr">
         <is>
-          <t>FLOW</t>
-        </is>
-      </c>
-      <c r="E115" s="22" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>MASTER_GRID</t>
+        </is>
+      </c>
+      <c r="E115" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F115" s="33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G115" s="23" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H115" s="25" t="inlineStr">
+        <is>
+          <t>Karthick</t>
+        </is>
+      </c>
+      <c r="I115" s="33" t="n">
         <v>0.75</v>
-      </c>
-      <c r="G115" s="23" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="H115" s="25" t="inlineStr">
-        <is>
-          <t>Karthick</t>
-        </is>
-      </c>
-      <c r="I115" s="33" t="n">
-        <v>1</v>
       </c>
       <c r="J115" s="24" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
       </c>
       <c r="K115" s="25" t="n"/>
       <c r="L115" s="33" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="M115" s="24" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
     </row>
     <row r="116">
       <c r="A116" s="32" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B116" s="25" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C116" s="25" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Blood Group</t>
         </is>
       </c>
       <c r="D116" s="25" t="inlineStr">
@@ -7517,7 +7517,7 @@
     </row>
     <row r="117">
       <c r="A117" s="32" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B117" s="25" t="inlineStr">
         <is>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="C117" s="25" t="inlineStr">
         <is>
-          <t>Blood Group</t>
+          <t>Currency Conversion</t>
         </is>
       </c>
       <c r="D117" s="25" t="inlineStr">
@@ -7573,7 +7573,7 @@
     </row>
     <row r="118">
       <c r="A118" s="32" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B118" s="25" t="inlineStr">
         <is>
@@ -7582,7 +7582,7 @@
       </c>
       <c r="C118" s="25" t="inlineStr">
         <is>
-          <t>Currency Conversion</t>
+          <t>Gender</t>
         </is>
       </c>
       <c r="D118" s="25" t="inlineStr">
@@ -7629,7 +7629,7 @@
     </row>
     <row r="119">
       <c r="A119" s="32" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B119" s="25" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="C119" s="25" t="inlineStr">
         <is>
-          <t>Gender</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="D119" s="25" t="inlineStr">
@@ -7685,7 +7685,7 @@
     </row>
     <row r="120">
       <c r="A120" s="32" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B120" s="25" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="C120" s="25" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Occupation</t>
         </is>
       </c>
       <c r="D120" s="25" t="inlineStr">
@@ -7741,7 +7741,7 @@
     </row>
     <row r="121">
       <c r="A121" s="32" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B121" s="25" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="C121" s="25" t="inlineStr">
         <is>
-          <t>Occupation</t>
+          <t>Payment Mode</t>
         </is>
       </c>
       <c r="D121" s="25" t="inlineStr">
@@ -7797,7 +7797,7 @@
     </row>
     <row r="122">
       <c r="A122" s="32" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B122" s="25" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
       </c>
       <c r="C122" s="25" t="inlineStr">
         <is>
-          <t>Payment Mode</t>
+          <t>Relation</t>
         </is>
       </c>
       <c r="D122" s="25" t="inlineStr">
@@ -7853,7 +7853,7 @@
     </row>
     <row r="123">
       <c r="A123" s="32" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B123" s="25" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
       </c>
       <c r="C123" s="25" t="inlineStr">
         <is>
-          <t>Relation</t>
+          <t>Salutation</t>
         </is>
       </c>
       <c r="D123" s="25" t="inlineStr">
@@ -7909,7 +7909,7 @@
     </row>
     <row r="124">
       <c r="A124" s="32" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B124" s="25" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
       </c>
       <c r="C124" s="25" t="inlineStr">
         <is>
-          <t>Salutation</t>
+          <t>City</t>
         </is>
       </c>
       <c r="D124" s="25" t="inlineStr">
@@ -7965,7 +7965,7 @@
     </row>
     <row r="125">
       <c r="A125" s="32" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B125" s="25" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
       </c>
       <c r="C125" s="25" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>Country</t>
         </is>
       </c>
       <c r="D125" s="25" t="inlineStr">
@@ -8021,7 +8021,7 @@
     </row>
     <row r="126">
       <c r="A126" s="32" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B126" s="25" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="C126" s="25" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t>District</t>
         </is>
       </c>
       <c r="D126" s="25" t="inlineStr">
@@ -8077,7 +8077,7 @@
     </row>
     <row r="127">
       <c r="A127" s="32" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B127" s="25" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
       </c>
       <c r="C127" s="25" t="inlineStr">
         <is>
-          <t>District</t>
+          <t>Locality</t>
         </is>
       </c>
       <c r="D127" s="25" t="inlineStr">
@@ -8133,7 +8133,7 @@
     </row>
     <row r="128">
       <c r="A128" s="32" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B128" s="25" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
       </c>
       <c r="C128" s="25" t="inlineStr">
         <is>
-          <t>Locality</t>
+          <t>Pincode</t>
         </is>
       </c>
       <c r="D128" s="25" t="inlineStr">
@@ -8189,7 +8189,7 @@
     </row>
     <row r="129">
       <c r="A129" s="32" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B129" s="25" t="inlineStr">
         <is>
@@ -8198,7 +8198,7 @@
       </c>
       <c r="C129" s="25" t="inlineStr">
         <is>
-          <t>Pincode</t>
+          <t>State</t>
         </is>
       </c>
       <c r="D129" s="25" t="inlineStr">
@@ -8245,30 +8245,30 @@
     </row>
     <row r="130">
       <c r="A130" s="32" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B130" s="25" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Reports</t>
         </is>
       </c>
       <c r="C130" s="25" t="inlineStr">
         <is>
-          <t>State</t>
+          <t>Generate Report</t>
         </is>
       </c>
       <c r="D130" s="25" t="inlineStr">
         <is>
-          <t>MASTER_GRID</t>
-        </is>
-      </c>
-      <c r="E130" s="27" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="E130" s="22" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F130" s="33" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G130" s="23" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         </is>
       </c>
       <c r="I130" s="33" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="J130" s="24" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="K130" s="25" t="n"/>
       <c r="L130" s="33" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="M130" s="24" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
     </row>
     <row r="131">
       <c r="A131" s="32" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B131" s="25" t="inlineStr">
         <is>
@@ -8310,12 +8310,12 @@
       </c>
       <c r="C131" s="25" t="inlineStr">
         <is>
-          <t>Generate Report</t>
+          <t>PowerBI Reports (combined: Report Master + User Mapping)</t>
         </is>
       </c>
       <c r="D131" s="25" t="inlineStr">
         <is>
-          <t>FLOW</t>
+          <t>Config</t>
         </is>
       </c>
       <c r="E131" s="22" t="inlineStr">
@@ -8324,20 +8324,20 @@
         </is>
       </c>
       <c r="F131" s="33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G131" s="24" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H131" s="25" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I131" s="33" t="n">
         <v>0.75</v>
-      </c>
-      <c r="G131" s="23" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="H131" s="25" t="inlineStr">
-        <is>
-          <t>Karthick</t>
-        </is>
-      </c>
-      <c r="I131" s="33" t="n">
-        <v>1</v>
       </c>
       <c r="J131" s="24" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
       </c>
       <c r="K131" s="25" t="n"/>
       <c r="L131" s="33" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="M131" s="24" t="inlineStr">
         <is>
@@ -8357,16 +8357,16 @@
     </row>
     <row r="132">
       <c r="A132" s="32" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B132" s="25" t="inlineStr">
         <is>
-          <t>Reports</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="C132" s="25" t="inlineStr">
         <is>
-          <t>PowerBI Reports (combined: Report Master + User Mapping)</t>
+          <t>SMS Setup</t>
         </is>
       </c>
       <c r="D132" s="25" t="inlineStr">
@@ -8380,20 +8380,20 @@
         </is>
       </c>
       <c r="F132" s="33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G132" s="24" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+        <v>0.75</v>
+      </c>
+      <c r="G132" s="23" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
       <c r="H132" s="25" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Karthick</t>
         </is>
       </c>
       <c r="I132" s="33" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="J132" s="24" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="K132" s="25" t="n"/>
       <c r="L132" s="33" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="M132" s="24" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
     </row>
     <row r="133">
       <c r="A133" s="32" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="B133" s="25" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
       </c>
       <c r="C133" s="25" t="inlineStr">
         <is>
-          <t>SMS Setup</t>
+          <t>Payment Gateways (combined: Per-Company + Gateway Master)</t>
         </is>
       </c>
       <c r="D133" s="25" t="inlineStr">
@@ -8438,14 +8438,14 @@
       <c r="F133" s="33" t="n">
         <v>0.75</v>
       </c>
-      <c r="G133" s="23" t="inlineStr">
-        <is>
-          <t>Completed</t>
+      <c r="G133" s="24" t="inlineStr">
+        <is>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="H133" s="25" t="inlineStr">
         <is>
-          <t>Karthick</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="I133" s="33" t="n">
@@ -8469,7 +8469,7 @@
     </row>
     <row r="134">
       <c r="A134" s="32" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B134" s="25" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="C134" s="25" t="inlineStr">
         <is>
-          <t>Payment Gateways (combined: Per-Company + Gateway Master)</t>
+          <t>Event Registration Page</t>
         </is>
       </c>
       <c r="D134" s="25" t="inlineStr">
@@ -8486,26 +8486,26 @@
           <t>Config</t>
         </is>
       </c>
-      <c r="E134" s="22" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="E134" s="29" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="F134" s="33" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G134" s="24" t="inlineStr">
-        <is>
-          <t>Not Started</t>
+        <v>1</v>
+      </c>
+      <c r="G134" s="23" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
       <c r="H134" s="25" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Karthick</t>
         </is>
       </c>
       <c r="I134" s="33" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J134" s="24" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
       </c>
       <c r="K134" s="25" t="n"/>
       <c r="L134" s="33" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M134" s="24" t="inlineStr">
         <is>
@@ -8525,7 +8525,7 @@
     </row>
     <row r="135">
       <c r="A135" s="32" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B135" s="25" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="C135" s="25" t="inlineStr">
         <is>
-          <t>Event Registration Page</t>
+          <t>P2P Campaign Pages</t>
         </is>
       </c>
       <c r="D135" s="25" t="inlineStr">
@@ -8581,7 +8581,7 @@
     </row>
     <row r="136">
       <c r="A136" s="32" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B136" s="25" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
       </c>
       <c r="C136" s="25" t="inlineStr">
         <is>
-          <t>P2P Campaign Pages</t>
+          <t>Prayer Request Page</t>
         </is>
       </c>
       <c r="D136" s="25" t="inlineStr">
@@ -8637,7 +8637,7 @@
     </row>
     <row r="137">
       <c r="A137" s="32" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B137" s="25" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
       </c>
       <c r="C137" s="25" t="inlineStr">
         <is>
-          <t>Prayer Request Page</t>
+          <t>Volunteer Registration Page</t>
         </is>
       </c>
       <c r="D137" s="25" t="inlineStr">
@@ -8693,7 +8693,7 @@
     </row>
     <row r="138">
       <c r="A138" s="32" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B138" s="25" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
       </c>
       <c r="C138" s="25" t="inlineStr">
         <is>
-          <t>Volunteer Registration Page</t>
+          <t>Crowdfunding Page</t>
         </is>
       </c>
       <c r="D138" s="25" t="inlineStr">
@@ -8746,62 +8746,6 @@
         </is>
       </c>
       <c r="N138" s="25" t="n"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="32" t="n">
-        <v>173</v>
-      </c>
-      <c r="B139" s="25" t="inlineStr">
-        <is>
-          <t>Settings</t>
-        </is>
-      </c>
-      <c r="C139" s="25" t="inlineStr">
-        <is>
-          <t>Crowdfunding Page</t>
-        </is>
-      </c>
-      <c r="D139" s="25" t="inlineStr">
-        <is>
-          <t>Config</t>
-        </is>
-      </c>
-      <c r="E139" s="29" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F139" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="G139" s="23" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="H139" s="25" t="inlineStr">
-        <is>
-          <t>Karthick</t>
-        </is>
-      </c>
-      <c r="I139" s="33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J139" s="24" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K139" s="25" t="n"/>
-      <c r="L139" s="33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M139" s="24" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N139" s="25" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
